--- a/outputs/commercial-quality/essential-supporting-register.xlsx
+++ b/outputs/commercial-quality/essential-supporting-register.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="1" r:id="Rff7f0db163b646d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="2" r:id="R23befce1d7c1424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="3" r:id="R89a225652dbd477d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="4" r:id="R1b48f8e6f98a4591"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="5" r:id="Rddbb6215682f455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Agenda" sheetId="6" r:id="R0b9ac5dbaa9a4c3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="R0ef7225deff643c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="R112ebff4a0ad46eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4fb10810d5de444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="R5cf82cdc45b04313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R11f8fbcf79034878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="4" r:id="Raecab667226546ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="5" r:id="R6cae350385664347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="6" r:id="R386285b7f29a4be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="R12911279fa404978"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="R800e50ed325044ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -72,7 +72,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FindingsTable" displayName="FindingsTable" ref="A1:R35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReadmeTable" displayName="ReadmeTable" ref="A1:C6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:C6"/>
+  <x:tableColumns count="3">
+    <x:tableColumn id="1" name="Field"/>
+    <x:tableColumn id="2" name="Meaning"/>
+    <x:tableColumn id="3" name="Boundary"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FindingsTable" displayName="FindingsTable" ref="A1:R35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:R35"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="Finding ID"/>
@@ -98,8 +110,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RisksTable" displayName="RisksTable" ref="A1:M32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RisksTable" displayName="RisksTable" ref="A1:M32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:M32"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="Risk ID"/>
@@ -120,8 +132,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ControlActionsTable" displayName="ControlActionsTable" ref="A1:Q35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ControlActionsTable" displayName="ControlActionsTable" ref="A1:Q35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:Q35"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="Control action ID"/>
@@ -146,8 +158,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceChecklistTable" displayName="EvidenceChecklistTable" ref="A1:I143" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="EvidenceChecklistTable" displayName="EvidenceChecklistTable" ref="A1:I143" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:I143"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Evidence ID"/>
@@ -164,8 +176,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="RoadmapTable" displayName="RoadmapTable" ref="A1:L35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RoadmapTable" displayName="RoadmapTable" ref="A1:L35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:L35"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Action ID"/>
@@ -180,19 +192,6 @@
     <x:tableColumn id="10" name="Linked risks"/>
     <x:tableColumn id="11" name="Success measure"/>
     <x:tableColumn id="12" name="Evidence of completion"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="FunctionalAgendaTable" displayName="FunctionalAgendaTable" ref="A1:D81" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D81"/>
-  <x:tableColumns count="4">
-    <x:tableColumn id="1" name="Agenda ID"/>
-    <x:tableColumn id="2" name="Function"/>
-    <x:tableColumn id="3" name="Question for the review"/>
-    <x:tableColumn id="4" name="Linked finding"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -435,1987 +434,78 @@
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="24" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="24" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Finding ID</x:v>
+        <x:v>Field</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Question code</x:v>
+        <x:v>Meaning</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Domain code</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>Domain</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>Control statement</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>Recorded response</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>Materiality class</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>Materiality score</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>Critical control</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>Hard gate</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
-        <x:v>Gap classification</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="str">
-        <x:v>Selection reasons</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="str">
-        <x:v>Diagnosis</x:v>
-      </x:c>
-      <x:c r="N1" s="3" t="str">
-        <x:v>Why it matters</x:v>
-      </x:c>
-      <x:c r="O1" s="3" t="str">
-        <x:v>Expected control standard</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="str">
-        <x:v>Recommended control</x:v>
-      </x:c>
-      <x:c r="Q1" s="3" t="str">
-        <x:v>Accountable owner</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="str">
-        <x:v>Target period</x:v>
+        <x:v>Boundary</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>MF-D1-Q04</x:v>
+        <x:v>Workbook purpose</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>D1-Q04</x:v>
+        <x:v>Essential fraud-readiness supporting register</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>D1</x:v>
-      </x:c>
-      <x:c r="D2" s="5" t="str">
-        <x:v>Fraud Leadership and Governance</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="str">
-        <x:v>Management owns fraud risk, while internal audit or assurance functions provide independent review where they exist.</x:v>
-      </x:c>
-      <x:c r="F2" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G2" s="5" t="str">
-        <x:v>maturity_constraint</x:v>
-      </x:c>
-      <x:c r="H2" s="5" t="n">
-        <x:v>2680</x:v>
-      </x:c>
-      <x:c r="I2" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J2" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K2" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L2" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; MATURITY_CAP_EVENT; CRITICAL_GAP; MAJOR_GAP</x:v>
-      </x:c>
-      <x:c r="M2" s="5" t="str">
-        <x:v>Management-versus-assurance role separation was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N2" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O2" s="5" t="str">
-        <x:v>Management designs and operates fraud controls; internal audit or another independent function periodically tests them and reports without assuming management responsibility.</x:v>
-      </x:c>
-      <x:c r="P2" s="5" t="str">
-        <x:v>The CEO and audit-committee chair must approve a RACI that assigns control operation to management and risk owners, reserves independent validation and unrestricted reporting for internal audit or equivalent assurance, and requires annual conflict review; the company secretary retains the approved RACI and minutes.</x:v>
-      </x:c>
-      <x:c r="Q2" s="5" t="str">
-        <x:v>CEO / Managing Director</x:v>
-      </x:c>
-      <x:c r="R2" s="5" t="str">
-        <x:v>30 days</x:v>
+        <x:v>Complete question, finding, evidence and action trace</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="str">
-        <x:v>MF-D3-Q03</x:v>
+        <x:v>Organisation</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>D3-Q03</x:v>
+        <x:v>Rivonia Health Logistics (Pty) Ltd</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>D3</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="str">
-        <x:v>Operational Fraud Controls</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="str">
-        <x:v>Supplier onboarding includes checks on business information, ownership, banking details or other fraud-risk indicators.</x:v>
-      </x:c>
-      <x:c r="F3" s="5" t="str">
-        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
-      </x:c>
-      <x:c r="G3" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H3" s="5" t="n">
-        <x:v>2660</x:v>
-      </x:c>
-      <x:c r="I3" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J3" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K3" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L3" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; ABSENT_CONTROL; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M3" s="5" t="str">
-        <x:v>Supplier-onboarding verification was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N3" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O3" s="5" t="str">
-        <x:v>Every supplier is verified against legal identity, ownership, tax/banking and risk indicators before activation, with enhanced review for high-risk suppliers.</x:v>
-      </x:c>
-      <x:c r="P3" s="5" t="str">
-        <x:v>Procurement performs a pre-activation checklist across every proposed supplier, independently verifies registration and bank ownership, screens beneficial owners and conflicts, risk-rates the supplier, and blocks ERP activation until a second reviewer signs; the vendor master retains the evidence package.</x:v>
-      </x:c>
-      <x:c r="Q3" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R3" s="5" t="str">
-        <x:v>60 days</x:v>
+        <x:v>Persisted assessment source</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="str">
-        <x:v>MF-D7-Q04</x:v>
+        <x:v>How to read it</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>D7-Q04</x:v>
+        <x:v>Customer-facing meaning comes first; technical references appear last.</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="str">
-        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="str">
-        <x:v>Supplier payment processes include checks to reduce invoice manipulation, fake vendors, bank-detail changes or vendor impersonation.</x:v>
-      </x:c>
-      <x:c r="F4" s="5" t="str">
-        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="n">
-        <x:v>2660</x:v>
-      </x:c>
-      <x:c r="I4" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J4" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K4" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L4" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; ABSENT_CONTROL; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M4" s="5" t="str">
-        <x:v>Supplier payment and bank-detail-change verification was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N4" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O4" s="5" t="str">
-        <x:v>Every bank-detail change is verified independently through a trusted pre-existing contact and segregated from payment approval; invoices are matched to approved supplier and purchasing records.</x:v>
-      </x:c>
-      <x:c r="P4" s="5" t="str">
-        <x:v>Accounts Payable quarantines every bank-detail change, retrieves a contact from the pre-change vendor master, completes and records an outbound callback, obtains second-person approval from someone outside vendor-master maintenance, blocks payment until verification, and gives the CFO a monthly report of all changes, failures and bypass attempts.</x:v>
-      </x:c>
-      <x:c r="Q4" s="5" t="str">
-        <x:v>CFO</x:v>
-      </x:c>
-      <x:c r="R4" s="5" t="str">
-        <x:v>30 days</x:v>
+        <x:v>Question Trace retains the complete response universe.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="str">
-        <x:v>MF-D5-Q05</x:v>
+        <x:v>Date convention</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>D5-Q05</x:v>
+        <x:v>DD MMM YYYY</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>D5</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="str">
-        <x:v>Fraud Incident Response</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="str">
-        <x:v>Evidence linked to suspected fraud is identified, preserved and handled appropriately.</x:v>
-      </x:c>
-      <x:c r="F5" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G5" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H5" s="5" t="n">
-        <x:v>2430</x:v>
-      </x:c>
-      <x:c r="I5" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J5" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K5" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L5" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M5" s="5" t="str">
-        <x:v>Fraud evidence preservation and chain of custody was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N5" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O5" s="5" t="str">
-        <x:v>Evidence is collected under legal direction where needed, hashed or sealed, logged through every transfer, access-restricted and retained under an approved schedule.</x:v>
-      </x:c>
-      <x:c r="P5" s="5" t="str">
-        <x:v>The investigation lead opens an evidence register for every material case; trained custodians identify sources, create forensic copies or sealed originals, record hashes/seal numbers, collector/time/location and every transfer, store evidence in access-controlled repositories, and escalate any custody break immediately to Legal.</x:v>
-      </x:c>
-      <x:c r="Q5" s="5" t="str">
-        <x:v>General Counsel / COO</x:v>
-      </x:c>
-      <x:c r="R5" s="5" t="str">
-        <x:v>60 days</x:v>
+        <x:v>No ISO timestamps in customer-facing cells</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="str">
-        <x:v>MF-D1-Q01</x:v>
+        <x:v>Status boundary</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>D1-Q01</x:v>
+        <x:v>Recorded self-assessment is not independent validation.</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>D1</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="str">
-        <x:v>Fraud Leadership and Governance</x:v>
-      </x:c>
-      <x:c r="E6" s="5" t="str">
-        <x:v>A named senior owner is accountable for fraud risk management and has authority to drive action.</x:v>
-      </x:c>
-      <x:c r="F6" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G6" s="5" t="str">
-        <x:v>maturity_constraint</x:v>
-      </x:c>
-      <x:c r="H6" s="5" t="n">
-        <x:v>2400</x:v>
-      </x:c>
-      <x:c r="I6" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J6" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K6" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L6" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; MATURITY_CAP_EVENT; CRITICAL_GAP</x:v>
-      </x:c>
-      <x:c r="M6" s="5" t="str">
-        <x:v>Senior fraud-risk ownership was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N6" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O6" s="5" t="str">
-        <x:v>A named senior executive owns the fraud-risk programme, its budget, unresolved exceptions and reporting to the governing body.</x:v>
-      </x:c>
-      <x:c r="P6" s="5" t="str">
-        <x:v>The CEO must issue a dated fraud-risk accountability mandate naming one executive, delegated decision rights, budget authority, quarterly reporting obligations and a 30-day escalation route for overdue control actions; the company secretary retains approvals and quarterly packs.</x:v>
-      </x:c>
-      <x:c r="Q6" s="5" t="str">
-        <x:v>CEO / Managing Director</x:v>
-      </x:c>
-      <x:c r="R6" s="5" t="str">
-        <x:v>30 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="5" t="str">
-        <x:v>MF-D4-Q01</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="str">
-        <x:v>D4-Q01</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="str">
-        <x:v>D4</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="str">
-        <x:v>Fraud Detection Capability</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="str">
-        <x:v>The organisation monitors transactions or operational activity for unusual patterns, anomalies or red flags.</x:v>
-      </x:c>
-      <x:c r="F7" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G7" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="n">
-        <x:v>2300</x:v>
-      </x:c>
-      <x:c r="I7" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J7" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K7" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L7" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M7" s="5" t="str">
-        <x:v>Transaction and activity monitoring was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N7" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O7" s="5" t="str">
-        <x:v>Defined monitoring covers the material transaction and activity population, uses risk-based indicators, and produces reviewable output on a set rhythm rather than relying on incidental discovery.</x:v>
-      </x:c>
-      <x:c r="P7" s="5" t="str">
-        <x:v>The monitoring owner must define red-flag indicators per material process — duplicate payments, round-value patterns, out-of-hours activity, unusual volume by user, adjustments reversing prior entries, and supplier or customer concentration — run them against the complete transaction population on a set rhythm, and route output into the exception queue with named reviewers and SLAs; coverage against the process fraud maps is reported to the fraud forum.</x:v>
-      </x:c>
-      <x:c r="Q7" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R7" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="5" t="str">
-        <x:v>MF-D8-Q01</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>D8-Q01</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>D8</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>Digital and Identity Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E8" s="5" t="str">
-        <x:v>The organisation verifies the identity of customers, users, employees, suppliers or counterparties where identity misuse could create fraud loss or harm.</x:v>
-      </x:c>
-      <x:c r="F8" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H8" s="5" t="n">
-        <x:v>2300</x:v>
-      </x:c>
-      <x:c r="I8" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J8" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K8" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L8" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M8" s="5" t="str">
-        <x:v>Identity verification at risk points was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N8" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O8" s="5" t="str">
-        <x:v>Identity verification is applied at defined risk points using independent sources proportionate to risk, with results recorded, exceptions approved and re-verification on sensitive change.</x:v>
-      </x:c>
-      <x:c r="P8" s="5" t="str">
-        <x:v>The process owner must define the risk points requiring verification — customer or beneficiary enrolment, employee onboarding, supplier activation and counterparty contracting — and apply proportionate checks against independent sources such as identity documents validated for authenticity, company registration records, and confirmation of contact details through independently obtained channels; results and evidence are retained under applicable data-protection obligations, exceptions require documented approval, and sensitive profile or banking changes trigger re-verification.</x:v>
-      </x:c>
-      <x:c r="Q8" s="5" t="str">
-        <x:v>COO / CFO</x:v>
-      </x:c>
-      <x:c r="R8" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="5" t="str">
-        <x:v>MF-D10-Q01</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>D10-Q01</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>D10</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>Continuous Improvement and Fraud Risk Monitoring</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="str">
-        <x:v>The organisation periodically reviews its fraud risks and control environment.</x:v>
-      </x:c>
-      <x:c r="F9" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G9" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="n">
-        <x:v>2220</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J9" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K9" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L9" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP</x:v>
-      </x:c>
-      <x:c r="M9" s="5" t="str">
-        <x:v>Periodic fraud risk and control environment review was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N9" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O9" s="5" t="str">
-        <x:v>A scheduled review reassesses fraud risks, tests whether key controls still operate as designed, and reports a consolidated position with owned actions to governance.</x:v>
-      </x:c>
-      <x:c r="P9" s="5" t="str">
-        <x:v>The Head of Risk must run a scheduled review that revisits the fraud risk assessment for continued relevance, confirms for each key control that it still has a named owner and is still operating by sampling recent evidence rather than accepting attestation, records any control that has lapsed or degraded, and reports a consolidated risk and control position to the governing body with owned remediation actions and due dates.</x:v>
-      </x:c>
-      <x:c r="Q9" s="5" t="str">
-        <x:v>CEO / Managing Director</x:v>
-      </x:c>
-      <x:c r="R9" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="5" t="str">
-        <x:v>MF-D2-Q01</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>D2-Q01</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>D2</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>Fraud Risk Identification</x:v>
-      </x:c>
-      <x:c r="E10" s="5" t="str">
-        <x:v>The organisation has completed a structured fraud risk assessment within the past two years.</x:v>
-      </x:c>
-      <x:c r="F10" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="n">
-        <x:v>2220</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J10" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K10" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L10" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP</x:v>
-      </x:c>
-      <x:c r="M10" s="5" t="str">
-        <x:v>Structured fraud risk assessment currency was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N10" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O10" s="5" t="str">
-        <x:v>A structured fraud risk assessment completed within the past two years covers the material processes, uses a repeatable method, rates inherent and residual risk, names owners and produces a tracked treatment plan.</x:v>
-      </x:c>
-      <x:c r="P10" s="5" t="str">
-        <x:v>The Head of Risk must run a documented fraud risk assessment at least every two years using a repeatable method: scope the material processes and channels, identify fraud scenarios per process with the roles able to execute them, rate likelihood and impact before and after existing controls, name a treatment owner and due date for every unacceptable residual risk, and obtain governing-body approval of the plan; assessment date, participants and method are retained.</x:v>
-      </x:c>
-      <x:c r="Q10" s="5" t="str">
-        <x:v>CEO / Managing Director</x:v>
-      </x:c>
-      <x:c r="R10" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="5" t="str">
-        <x:v>MF-D3-Q04</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>D3-Q04</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>D3</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>Operational Fraud Controls</x:v>
-      </x:c>
-      <x:c r="E11" s="5" t="str">
-        <x:v>System and data access are granted based on role requirements and reviewed periodically.</x:v>
-      </x:c>
-      <x:c r="F11" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G11" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H11" s="5" t="n">
-        <x:v>2150</x:v>
-      </x:c>
-      <x:c r="I11" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J11" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K11" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L11" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M11" s="5" t="str">
-        <x:v>Role-based user-access governance was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N11" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O11" s="5" t="str">
-        <x:v>All in-scope user access maps to an approved role, is reviewed by the business owner each quarter and is removed promptly after role change or exit.</x:v>
-      </x:c>
-      <x:c r="P11" s="5" t="str">
-        <x:v>System owners export the complete active-user population quarterly; line managers compare every entitlement to the approved role matrix, record keep/remove decisions, and route exceptions to IT for closure within 10 business days; Risk samples completed reviews and overdue removals are escalated to the COO.</x:v>
-      </x:c>
-      <x:c r="Q11" s="5" t="str">
-        <x:v>COO</x:v>
-      </x:c>
-      <x:c r="R11" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="5" t="str">
-        <x:v>MF-D5-Q01</x:v>
-      </x:c>
-      <x:c r="B12" s="5" t="str">
-        <x:v>D5-Q01</x:v>
-      </x:c>
-      <x:c r="C12" s="5" t="str">
-        <x:v>D5</x:v>
-      </x:c>
-      <x:c r="D12" s="5" t="str">
-        <x:v>Fraud Incident Response</x:v>
-      </x:c>
-      <x:c r="E12" s="5" t="str">
-        <x:v>The organisation has a documented process for responding to suspected fraud incidents.</x:v>
-      </x:c>
-      <x:c r="F12" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G12" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H12" s="5" t="n">
-        <x:v>2150</x:v>
-      </x:c>
-      <x:c r="I12" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J12" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K12" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L12" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M12" s="5" t="str">
-        <x:v>Fraud incident-response governance was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N12" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O12" s="5" t="str">
-        <x:v>A documented plan defines intake, severity, command roles, containment, legal/evidence decisions, communications and closure, and is rehearsed annually.</x:v>
-      </x:c>
-      <x:c r="P12" s="5" t="str">
-        <x:v>The incident-response lead maintains a version-controlled plan covering every reported fraud incident, names an incident commander and deputies, classifies severity at intake, convenes Legal/HR/IT/Finance roles, records decisions and containment actions, and runs an annual tabletop with tracked remediation.</x:v>
-      </x:c>
-      <x:c r="Q12" s="5" t="str">
-        <x:v>COO / General Counsel</x:v>
-      </x:c>
-      <x:c r="R12" s="5" t="str">
-        <x:v>30 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="5" t="str">
-        <x:v>MF-D8-Q02</x:v>
-      </x:c>
-      <x:c r="B13" s="5" t="str">
-        <x:v>D8-Q02</x:v>
-      </x:c>
-      <x:c r="C13" s="5" t="str">
-        <x:v>D8</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="str">
-        <x:v>Digital and Identity Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E13" s="5" t="str">
-        <x:v>Systems or digital platforms are monitored for suspicious activity such as unusual login, access, profile, transaction or account behaviour.</x:v>
-      </x:c>
-      <x:c r="F13" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G13" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H13" s="5" t="n">
-        <x:v>2150</x:v>
-      </x:c>
-      <x:c r="I13" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J13" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K13" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L13" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M13" s="5" t="str">
-        <x:v>Suspicious digital-activity monitoring was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N13" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O13" s="5" t="str">
-        <x:v>Risk-based monitoring covers material digital events, alerts are triaged to defined SLAs and rules are tuned from confirmed outcomes.</x:v>
-      </x:c>
-      <x:c r="P13" s="5" t="str">
-        <x:v>The security monitoring owner inventories material login, privilege, profile and transaction events, implements risk rules across the full in-scope event feed, assigns alerts to trained analysts, preserves dispositions and escalates high-risk account compromise immediately; monthly tuning uses confirmed true/false positives.</x:v>
-      </x:c>
-      <x:c r="Q13" s="5" t="str">
-        <x:v>Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="R13" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="5" t="str">
-        <x:v>MF-D8-Q04</x:v>
-      </x:c>
-      <x:c r="B14" s="5" t="str">
-        <x:v>D8-Q04</x:v>
-      </x:c>
-      <x:c r="C14" s="5" t="str">
-        <x:v>D8</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="str">
-        <x:v>Digital and Identity Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E14" s="5" t="str">
-        <x:v>Access to sensitive digital systems, administrator rights and confidential data is restricted and reviewed.</x:v>
-      </x:c>
-      <x:c r="F14" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G14" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H14" s="5" t="n">
-        <x:v>2150</x:v>
-      </x:c>
-      <x:c r="I14" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J14" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K14" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L14" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M14" s="5" t="str">
-        <x:v>Privileged and administrator access governance was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N14" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O14" s="5" t="str">
-        <x:v>Every privileged account is named, justified, least-privileged, strongly authenticated, logged and independently recertified quarterly; emergency access expires automatically.</x:v>
-      </x:c>
-      <x:c r="P14" s="5" t="str">
-        <x:v>IT Security maintains a complete privileged-account register, links each human and service account to an owner and approved justification, enforces separate named admin identities and MFA, records privileged sessions, and sends the full population quarterly to system owners and Risk for independent keep/remove certification; removals close within 24 hours for leavers and five business days otherwise.</x:v>
-      </x:c>
-      <x:c r="Q14" s="5" t="str">
-        <x:v>Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="R14" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="5" t="str">
-        <x:v>MF-D4-Q03</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="str">
-        <x:v>D4-Q03</x:v>
-      </x:c>
-      <x:c r="C15" s="5" t="str">
-        <x:v>D4</x:v>
-      </x:c>
-      <x:c r="D15" s="5" t="str">
-        <x:v>Fraud Detection Capability</x:v>
-      </x:c>
-      <x:c r="E15" s="5" t="str">
-        <x:v>Analytics, rules, reports or data checks are used to identify suspicious transactions, behaviour or control exceptions.</x:v>
-      </x:c>
-      <x:c r="F15" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G15" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H15" s="5" t="n">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c r="I15" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J15" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K15" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L15" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M15" s="5" t="str">
-        <x:v>Analytics and rule-based detection was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N15" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O15" s="5" t="str">
-        <x:v>A maintained catalogue of rules and data checks maps each validate to a fraud scenario, runs against reconciled data, and is tuned from confirmed outcomes.</x:v>
-      </x:c>
-      <x:c r="P15" s="5" t="str">
-        <x:v>The monitoring owner must maintain a rule catalogue in which every validate names the fraud scenario it addresses, the data source, the threshold and the reviewing role; tests include duplicate and near-duplicate payments, supplier and employee bank-detail or address matches, unusual approval pairings, dormant-account reactivation and threshold-adjacent transaction clustering; results reconcile to source control totals and rules are tuned monthly from confirmed true and false positives.</x:v>
-      </x:c>
-      <x:c r="Q15" s="5" t="str">
-        <x:v>CFO / Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="R15" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="5" t="str">
-        <x:v>MF-D8-Q08</x:v>
-      </x:c>
-      <x:c r="B16" s="5" t="str">
-        <x:v>D8-Q08</x:v>
-      </x:c>
-      <x:c r="C16" s="5" t="str">
-        <x:v>D8</x:v>
-      </x:c>
-      <x:c r="D16" s="5" t="str">
-        <x:v>Digital and Identity Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E16" s="5" t="str">
-        <x:v>The organisation can detect or investigate identity misuse, account takeover, impersonation or unauthorised profile changes where relevant.</x:v>
-      </x:c>
-      <x:c r="F16" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G16" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H16" s="5" t="n">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c r="I16" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J16" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K16" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L16" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M16" s="5" t="str">
-        <x:v>Identity misuse detection and investigation capability was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N16" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O16" s="5" t="str">
-        <x:v>Sufficient logging, alerting and investigative capability exists to identify compromise, reconstruct what occurred, contain it and support recovery or referral.</x:v>
-      </x:c>
-      <x:c r="P16" s="5" t="str">
-        <x:v>The security operations owner must ensure authentication events, credential and multi-factor changes, profile and banking-detail changes, device and session identifiers and transaction history are logged for all material identity-bearing systems and retained for a defined period consistent with data-protection obligations; alerting covers impossible-travel and anomalous login, credential and contact-detail change followed by transaction, and dormant-account reactivation, with an investigation runbook defining containment such as session revocation and forced credential reset.</x:v>
-      </x:c>
-      <x:c r="Q16" s="5" t="str">
-        <x:v>Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="R16" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="5" t="str">
-        <x:v>MF-D2-Q02</x:v>
-      </x:c>
-      <x:c r="B17" s="5" t="str">
-        <x:v>D2-Q02</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="str">
-        <x:v>D2</x:v>
-      </x:c>
-      <x:c r="D17" s="5" t="str">
-        <x:v>Fraud Risk Identification</x:v>
-      </x:c>
-      <x:c r="E17" s="5" t="str">
-        <x:v>Fraud risks have been mapped across important processes such as procurement, payments, refunds, claims, stock, supplier management or service delivery.</x:v>
-      </x:c>
-      <x:c r="F17" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G17" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H17" s="5" t="n">
-        <x:v>1940</x:v>
-      </x:c>
-      <x:c r="I17" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J17" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="K17" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L17" s="5" t="str">
-        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP</x:v>
-      </x:c>
-      <x:c r="M17" s="5" t="str">
-        <x:v>Process-level fraud risk mapping was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N17" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
-      </x:c>
-      <x:c r="O17" s="5" t="str">
-        <x:v>Each material process — procurement, payments, refunds, claims, stock, supplier management and service delivery as applicable — has documented fraud scenarios, the roles able to execute them, and the controls relied upon.</x:v>
-      </x:c>
-      <x:c r="P17" s="5" t="str">
-        <x:v>The Head of Risk must produce a process-by-process fraud map covering every material value-bearing process: for each, record the fraud scenarios, the roles and system permissions able to execute them alone or in collusion, the preventive and detective controls relied upon, and the residual gap; process owners sign their own map, and any process without a mapped control owner escalates to the fraud-risk executive.</x:v>
-      </x:c>
-      <x:c r="Q17" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R17" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="5" t="str">
-        <x:v>MF-D7-Q01</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="str">
-        <x:v>D7-Q01</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="str">
-        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E18" s="5" t="str">
-        <x:v>Suppliers, contractors or other third parties are subject to due diligence before being engaged.</x:v>
-      </x:c>
-      <x:c r="F18" s="5" t="str">
-        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
-      </x:c>
-      <x:c r="G18" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H18" s="5" t="n">
-        <x:v>1480</x:v>
-      </x:c>
-      <x:c r="I18" s="5" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J18" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K18" s="5" t="str">
-        <x:v>critical</x:v>
-      </x:c>
-      <x:c r="L18" s="5" t="str">
-        <x:v>CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; ABSENT_CONTROL; WEAKEST_DOMAIN; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
-      </x:c>
-      <x:c r="M18" s="5" t="str">
-        <x:v>Third-party pre-engagement due diligence was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N18" s="5" t="str">
-        <x:v>This recorded weakness affects a methodology critical control and warrants priority treatment.</x:v>
-      </x:c>
-      <x:c r="O18" s="5" t="str">
-        <x:v>All third parties receive proportionate identity, ownership, sanctions/conflict and capability checks before contracting, with enhanced approval for high-risk relationships.</x:v>
-      </x:c>
-      <x:c r="P18" s="5" t="str">
-        <x:v>The vendor-risk owner risk-rates every proposed third party, verifies legal identity and beneficial ownership from independent sources, screens sanctions/adverse and employee conflicts, documents capability and bank ownership, and requires Compliance approval for high-risk cases before contract signature or system activation.</x:v>
-      </x:c>
-      <x:c r="Q18" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R18" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="5" t="str">
-        <x:v>MF-D4-Q02</x:v>
-      </x:c>
-      <x:c r="B19" s="5" t="str">
-        <x:v>D4-Q02</x:v>
-      </x:c>
-      <x:c r="C19" s="5" t="str">
-        <x:v>D4</x:v>
-      </x:c>
-      <x:c r="D19" s="5" t="str">
-        <x:v>Fraud Detection Capability</x:v>
-      </x:c>
-      <x:c r="E19" s="5" t="str">
-        <x:v>Exception reports or alerts highlighting unusual transactions or activities are generated and reviewed regularly.</x:v>
-      </x:c>
-      <x:c r="F19" s="5" t="str">
-        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
-      </x:c>
-      <x:c r="G19" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H19" s="5" t="n">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="I19" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J19" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K19" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L19" s="5" t="str">
-        <x:v>ABSENT_CONTROL; WEAKEST_DOMAIN; CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M19" s="5" t="str">
-        <x:v>Exception-report review was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N19" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O19" s="5" t="str">
-        <x:v>The complete alert population is assigned, triaged to risk-based SLAs, dispositioned with evidence and independently reviewed for ageing and quality.</x:v>
-      </x:c>
-      <x:c r="P19" s="5" t="str">
-        <x:v>The monitoring owner generates a complete daily or weekly exception queue, assigns each alert to a trained reviewer, records investigation evidence and disposition, and escalates high-risk alerts immediately and all overdue alerts weekly; Risk performs a monthly closure-quality sample.</x:v>
-      </x:c>
-      <x:c r="Q19" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R19" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="5" t="str">
-        <x:v>MF-D10-Q04</x:v>
-      </x:c>
-      <x:c r="B20" s="5" t="str">
-        <x:v>D10-Q04</x:v>
-      </x:c>
-      <x:c r="C20" s="5" t="str">
-        <x:v>D10</x:v>
-      </x:c>
-      <x:c r="D20" s="5" t="str">
-        <x:v>Continuous Improvement and Fraud Risk Monitoring</x:v>
-      </x:c>
-      <x:c r="E20" s="5" t="str">
-        <x:v>The organisation monitors fraud trends affecting its sector, geography, customer environment or supplier base.</x:v>
-      </x:c>
-      <x:c r="F20" s="5" t="str">
-        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
-      </x:c>
-      <x:c r="G20" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H20" s="5" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="I20" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J20" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K20" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L20" s="5" t="str">
-        <x:v>ABSENT_CONTROL; WEAKEST_DOMAIN</x:v>
-      </x:c>
-      <x:c r="M20" s="5" t="str">
-        <x:v>Fraud trend monitoring across sector and environment was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N20" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O20" s="5" t="str">
-        <x:v>External trend monitoring is assigned, run on a defined rhythm, compared against internal loss and incident patterns, and reported with implications for control priorities.</x:v>
-      </x:c>
-      <x:c r="P20" s="5" t="str">
-        <x:v>The Head of Risk must assign trend monitoring across the sector, operating geographies, customer environment and supplier base using industry, insurer, law-enforcement and peer sources, compare external trends against the organisation’s own incident and loss data to identify both matches and gaps, and report each cycle with an explicit implication for control priorities and the treatment plan.</x:v>
-      </x:c>
-      <x:c r="Q20" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="R20" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="5" t="str">
-        <x:v>MF-D4-Q06</x:v>
-      </x:c>
-      <x:c r="B21" s="5" t="str">
-        <x:v>D4-Q06</x:v>
-      </x:c>
-      <x:c r="C21" s="5" t="str">
-        <x:v>D4</x:v>
-      </x:c>
-      <x:c r="D21" s="5" t="str">
-        <x:v>Fraud Detection Capability</x:v>
-      </x:c>
-      <x:c r="E21" s="5" t="str">
-        <x:v>People responsible for monitoring suspicious activity know when to escalate concerns and have authority to do so.</x:v>
-      </x:c>
-      <x:c r="F21" s="5" t="str">
-        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
-      </x:c>
-      <x:c r="G21" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H21" s="5" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="I21" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J21" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K21" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L21" s="5" t="str">
-        <x:v>ABSENT_CONTROL; CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M21" s="5" t="str">
-        <x:v>Escalation authority for monitoring staff was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N21" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O21" s="5" t="str">
-        <x:v>Written escalation criteria, routes and timeframes are defined, staff are trained on them, and escalation can bypass any implicated line manager.</x:v>
-      </x:c>
-      <x:c r="P21" s="5" t="str">
-        <x:v>The Head of Risk must publish escalation criteria defining what must be escalated, to whom and within what time, grant monitoring staff explicit authority to escalate directly to the fraud-risk executive or audit-committee chair where a manager is implicated, protect escalators from retaliation, train the monitoring team annually, and review escalation timeliness against criteria each quarter.</x:v>
-      </x:c>
-      <x:c r="Q21" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="R21" s="5" t="str">
-        <x:v>30 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="5" t="str">
-        <x:v>MF-D2-Q06</x:v>
-      </x:c>
-      <x:c r="B22" s="5" t="str">
-        <x:v>D2-Q06</x:v>
-      </x:c>
-      <x:c r="C22" s="5" t="str">
-        <x:v>D2</x:v>
-      </x:c>
-      <x:c r="D22" s="5" t="str">
-        <x:v>Fraud Risk Identification</x:v>
-      </x:c>
-      <x:c r="E22" s="5" t="str">
-        <x:v>The organisation monitors emerging fraud threats affecting its industry, geography or operating environment.</x:v>
-      </x:c>
-      <x:c r="F22" s="5" t="str">
-        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
-      </x:c>
-      <x:c r="G22" s="5" t="str">
-        <x:v>control_failure</x:v>
-      </x:c>
-      <x:c r="H22" s="5" t="n">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="I22" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J22" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K22" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L22" s="5" t="str">
-        <x:v>ABSENT_CONTROL</x:v>
-      </x:c>
-      <x:c r="M22" s="5" t="str">
-        <x:v>Emerging fraud-threat monitoring was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N22" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O22" s="5" t="str">
-        <x:v>Named sources are monitored on a defined rhythm, relevance is assessed against the organisation’s processes and channels, and material threats generate a control review or an explicit accept decision.</x:v>
-      </x:c>
-      <x:c r="P22" s="5" t="str">
-        <x:v>The Head of Risk must assign responsibility for monitoring a named source set covering industry associations, insurer and broker briefings, regional law-enforcement and regulator advisories, peer and supplier incident reports and relevant local crime patterns; each cycle threats are logged, assessed for relevance to the organisation’s processes, channels and geographies, and either raised as a control review with an owner or recorded as an explicit accept decision with rationale.</x:v>
-      </x:c>
-      <x:c r="Q22" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="R22" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="5" t="str">
-        <x:v>MF-D4-Q04</x:v>
-      </x:c>
-      <x:c r="B23" s="5" t="str">
-        <x:v>D4-Q04</x:v>
-      </x:c>
-      <x:c r="C23" s="5" t="str">
-        <x:v>D4</x:v>
-      </x:c>
-      <x:c r="D23" s="5" t="str">
-        <x:v>Fraud Detection Capability</x:v>
-      </x:c>
-      <x:c r="E23" s="5" t="str">
-        <x:v>Detection controls are updated when new fraud risks, fraud methods or operational changes emerge.</x:v>
-      </x:c>
-      <x:c r="F23" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G23" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H23" s="5" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="I23" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J23" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K23" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L23" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M23" s="5" t="str">
-        <x:v>Detection control currency was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N23" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O23" s="5" t="str">
-        <x:v>Defined triggers require detection rules and indicators to be reassessed, with changes recorded, validated before deployment and reported to the fraud forum.</x:v>
-      </x:c>
-      <x:c r="P23" s="5" t="str">
-        <x:v>The monitoring owner must reassess the detection set whenever a new fraud method is identified internally or externally, a material process or system changes, or a confirmed incident bypassed existing detection; each change is documented with rationale, validated against historical data before deployment, version-controlled, and reported with before-and-after coverage to the fraud forum.</x:v>
-      </x:c>
-      <x:c r="Q23" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R23" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="5" t="str">
-        <x:v>MF-D4-Q05</x:v>
-      </x:c>
-      <x:c r="B24" s="5" t="str">
-        <x:v>D4-Q05</x:v>
-      </x:c>
-      <x:c r="C24" s="5" t="str">
-        <x:v>D4</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="str">
-        <x:v>Fraud Detection Capability</x:v>
-      </x:c>
-      <x:c r="E24" s="5" t="str">
-        <x:v>Monitoring covers both internal misuse and external fraud threats where these are relevant to the organisation.</x:v>
-      </x:c>
-      <x:c r="F24" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G24" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H24" s="5" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="I24" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J24" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K24" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L24" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M24" s="5" t="str">
-        <x:v>Internal and external threat monitoring coverage was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N24" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O24" s="5" t="str">
-        <x:v>Monitoring explicitly addresses employee and insider misuse alongside external attack, with indicators, data sources and reviewers defined for both.</x:v>
-      </x:c>
-      <x:c r="P24" s="5" t="str">
-        <x:v>The monitoring owner must maintain a coverage matrix showing, for each material process, the indicators addressing internal misuse — override use, permission changes, adjustments by approvers, out-of-hours access — and those addressing external threats such as supplier impersonation, customer identity misuse and channel abuse; gaps in either column are logged with an owner, and coverage is reported to the fraud forum each cycle.</x:v>
-      </x:c>
-      <x:c r="Q24" s="5" t="str">
-        <x:v>CFO / Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="R24" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="5" t="str">
-        <x:v>MF-D5-Q02</x:v>
-      </x:c>
-      <x:c r="B25" s="5" t="str">
-        <x:v>D5-Q02</x:v>
-      </x:c>
-      <x:c r="C25" s="5" t="str">
-        <x:v>D5</x:v>
-      </x:c>
-      <x:c r="D25" s="5" t="str">
-        <x:v>Fraud Incident Response</x:v>
-      </x:c>
-      <x:c r="E25" s="5" t="str">
-        <x:v>Employees know where and how to report suspected fraud or misconduct.</x:v>
-      </x:c>
-      <x:c r="F25" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G25" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H25" s="5" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="I25" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J25" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K25" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L25" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M25" s="5" t="str">
-        <x:v>Workforce awareness of fraud reporting routes was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N25" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O25" s="5" t="str">
-        <x:v>Reporting routes are published in plain language, reach the entire workforce including non-desk and contract staff, and awareness is periodically validated rather than assumed.</x:v>
-      </x:c>
-      <x:c r="P25" s="5" t="str">
-        <x:v>The ethics owner must publish reporting routes in plain language across the channels the workforce actually uses — induction packs, payslip inserts, notice boards at depots and sites, intranet and supervisor briefings — covering line manager, confidential channel and conflict-free alternate route; awareness is validated periodically by short survey or spot check, and results below threshold trigger a targeted re-communication for the affected sites or teams.</x:v>
-      </x:c>
-      <x:c r="Q25" s="5" t="str">
-        <x:v>Chief People Officer / COO</x:v>
-      </x:c>
-      <x:c r="R25" s="5" t="str">
-        <x:v>30 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="5" t="str">
-        <x:v>MF-D7-Q03</x:v>
-      </x:c>
-      <x:c r="B26" s="5" t="str">
-        <x:v>D7-Q03</x:v>
-      </x:c>
-      <x:c r="C26" s="5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="D26" s="5" t="str">
-        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E26" s="5" t="str">
-        <x:v>Employees are required to disclose and manage conflicts of interest involving suppliers or third parties.</x:v>
-      </x:c>
-      <x:c r="F26" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G26" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H26" s="5" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="I26" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J26" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K26" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L26" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M26" s="5" t="str">
-        <x:v>Conflict of interest declaration and management was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N26" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O26" s="5" t="str">
-        <x:v>Declarations are collected from all staff able to influence supplier selection or payment, refreshed periodically and on change, validated against supplier data, and each declared conflict carries a documented management action.</x:v>
-      </x:c>
-      <x:c r="P26" s="5" t="str">
-        <x:v>The compliance owner must require annual and on-change declarations from every employee able to influence supplier selection, contracting, receipting or payment, covering directorships, shareholdings, family relationships and outside interests; declarations are validated against the vendor master for matching surnames, addresses, contact details and bank accounts, and every declared or detected conflict receives a documented management action such as recusal, reassignment or enhanced review, recorded in a conflict register.</x:v>
-      </x:c>
-      <x:c r="Q26" s="5" t="str">
-        <x:v>CFO / General Counsel</x:v>
-      </x:c>
-      <x:c r="R26" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="5" t="str">
-        <x:v>MF-D7-Q07</x:v>
-      </x:c>
-      <x:c r="B27" s="5" t="str">
-        <x:v>D7-Q07</x:v>
-      </x:c>
-      <x:c r="C27" s="5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="D27" s="5" t="str">
-        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E27" s="5" t="str">
-        <x:v>Fraud risks are considered when using agents, brokers, distributors, intermediaries, partners or outsourced service providers where relevant.</x:v>
-      </x:c>
-      <x:c r="F27" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G27" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H27" s="5" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="I27" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J27" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K27" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L27" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M27" s="5" t="str">
-        <x:v>Intermediary and outsourced provider fraud oversight was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N27" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O27" s="5" t="str">
-        <x:v>Intermediary and outsourced arrangements carry contractual fraud-control obligations, audit and information rights, defined oversight of delegated authority, and periodic assurance over the provider’s own controls.</x:v>
-      </x:c>
-      <x:c r="P27" s="5" t="str">
-        <x:v>The relationship owner must ensure every intermediary or outsourced arrangement defines in contract the fraud-control obligations, the limits of delegated authority, the right to audit and obtain records, incident-notification duties and consequences for breach; oversight includes reconciliation of transactions and collections handled on the organisation’s behalf, periodic assurance over the provider’s relevant controls, and review of any sub-contracting before it occurs.</x:v>
-      </x:c>
-      <x:c r="Q27" s="5" t="str">
-        <x:v>COO / CFO</x:v>
-      </x:c>
-      <x:c r="R27" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="5" t="str">
-        <x:v>MF-D8-Q03</x:v>
-      </x:c>
-      <x:c r="B28" s="5" t="str">
-        <x:v>D8-Q03</x:v>
-      </x:c>
-      <x:c r="C28" s="5" t="str">
-        <x:v>D8</x:v>
-      </x:c>
-      <x:c r="D28" s="5" t="str">
-        <x:v>Digital and Identity Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E28" s="5" t="str">
-        <x:v>Employees receive training on phishing, social engineering and digital impersonation attempts.</x:v>
-      </x:c>
-      <x:c r="F28" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G28" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H28" s="5" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="I28" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J28" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K28" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L28" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M28" s="5" t="str">
-        <x:v>Phishing and social-engineering awareness was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N28" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O28" s="5" t="str">
-        <x:v>Training is role-relevant, reinforced by periodic simulations, measured by behaviour rather than completion alone, and supported by a fast reporting route with feedback.</x:v>
-      </x:c>
-      <x:c r="P28" s="5" t="str">
-        <x:v>The security awareness owner must deliver role-relevant training covering payment-instruction and bank-detail-change requests, executive impersonation, urgency and secrecy pressure, credential-harvesting pages and voice or messaging impersonation; reinforce with periodic simulations targeted at high-risk roles such as finance and procurement, measure report rate as well as click rate, provide a one-click reporting route with feedback, and require verification through an independently obtained channel for any payment or bank-detail instruction.</x:v>
-      </x:c>
-      <x:c r="Q28" s="5" t="str">
-        <x:v>Chief Technology Officer / Chief People Officer</x:v>
-      </x:c>
-      <x:c r="R28" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="5" t="str">
-        <x:v>MF-D8-Q07</x:v>
-      </x:c>
-      <x:c r="B29" s="5" t="str">
-        <x:v>D8-Q07</x:v>
-      </x:c>
-      <x:c r="C29" s="5" t="str">
-        <x:v>D8</x:v>
-      </x:c>
-      <x:c r="D29" s="5" t="str">
-        <x:v>Digital and Identity Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E29" s="5" t="str">
-        <x:v>Emerging digital fraud risks relevant to the organisation's operations or sector are reviewed periodically.</x:v>
-      </x:c>
-      <x:c r="F29" s="5" t="str">
-        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
-      </x:c>
-      <x:c r="G29" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H29" s="5" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="I29" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J29" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K29" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L29" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M29" s="5" t="str">
-        <x:v>Emerging digital fraud risk review was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N29" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O29" s="5" t="str">
-        <x:v>Digital threat review runs on a defined cycle covering channel-specific attack methods, assesses them against current controls, and produces owned actions or explicit accept decisions.</x:v>
-      </x:c>
-      <x:c r="P29" s="5" t="str">
-        <x:v>The information security and digital owners must jointly run a periodic review of emerging digital fraud methods relevant to the organisation’s channels, drawing on vendor and industry advisories, incident experience and peer reporting; each method is assessed against current preventive and detective controls, gaps become owned actions with due dates, and accepted risks are recorded with rationale and reported to the risk forum.</x:v>
-      </x:c>
-      <x:c r="Q29" s="5" t="str">
-        <x:v>Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="R29" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="5" t="str">
-        <x:v>MF-D4-Q07</x:v>
-      </x:c>
-      <x:c r="B30" s="5" t="str">
-        <x:v>D4-Q07</x:v>
-      </x:c>
-      <x:c r="C30" s="5" t="str">
-        <x:v>D4</x:v>
-      </x:c>
-      <x:c r="D30" s="5" t="str">
-        <x:v>Fraud Detection Capability</x:v>
-      </x:c>
-      <x:c r="E30" s="5" t="str">
-        <x:v>Detection controls are periodically reviewed for effectiveness by management, risk, audit or another independent reviewer.</x:v>
-      </x:c>
-      <x:c r="F30" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G30" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H30" s="5" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="I30" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J30" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K30" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L30" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M30" s="5" t="str">
-        <x:v>Independent review of detection effectiveness was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N30" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O30" s="5" t="str">
-        <x:v>A reviewer independent of the monitoring team periodically evaluates detection coverage, output quality and closure integrity, and reports findings to governance.</x:v>
-      </x:c>
-      <x:c r="P30" s="5" t="str">
-        <x:v>The audit committee must commission a periodic independent evaluation of detection effectiveness covering coverage against the process fraud maps, data completeness, sample retesting of closed alerts for closure quality, and detection of deliberately seeded validate conditions where practical; findings are reported to governance with owners and due dates, and remediation is tracked to closure.</x:v>
-      </x:c>
-      <x:c r="Q30" s="5" t="str">
-        <x:v>Audit Committee Chair</x:v>
-      </x:c>
-      <x:c r="R30" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="5" t="str">
-        <x:v>MF-D5-Q04</x:v>
-      </x:c>
-      <x:c r="B31" s="5" t="str">
-        <x:v>D5-Q04</x:v>
-      </x:c>
-      <x:c r="C31" s="5" t="str">
-        <x:v>D5</x:v>
-      </x:c>
-      <x:c r="D31" s="5" t="str">
-        <x:v>Fraud Incident Response</x:v>
-      </x:c>
-      <x:c r="E31" s="5" t="str">
-        <x:v>Fraud investigations follow procedures that protect confidentiality, fairness, evidence and documentation.</x:v>
-      </x:c>
-      <x:c r="F31" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G31" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H31" s="5" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="I31" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J31" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K31" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L31" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M31" s="5" t="str">
-        <x:v>Investigation procedure and fairness was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N31" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O31" s="5" t="str">
-        <x:v>Written investigation procedures govern confidentiality, subject fairness, interview conduct, documentation standards and legal privilege considerations, and investigators are competent to apply them.</x:v>
-      </x:c>
-      <x:c r="P31" s="5" t="str">
-        <x:v>The investigation lead must maintain written procedures covering need-to-know confidentiality and case access restriction, the subject’s right to respond at the appropriate stage, interview conduct and record standards, contemporaneous documentation with dated file notes, retention and legal-privilege handling in consultation with Legal, and use of competent or accredited investigators; case files are quality-reviewed at closure against the procedure.</x:v>
-      </x:c>
-      <x:c r="Q31" s="5" t="str">
-        <x:v>General Counsel / COO</x:v>
-      </x:c>
-      <x:c r="R31" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="5" t="str">
-        <x:v>MF-D7-Q02</x:v>
-      </x:c>
-      <x:c r="B32" s="5" t="str">
-        <x:v>D7-Q02</x:v>
-      </x:c>
-      <x:c r="C32" s="5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="D32" s="5" t="str">
-        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E32" s="5" t="str">
-        <x:v>Procurement processes include safeguards against collusion, manipulation, bid rigging or favouritism.</x:v>
-      </x:c>
-      <x:c r="F32" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G32" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H32" s="5" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="I32" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J32" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K32" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L32" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M32" s="5" t="str">
-        <x:v>Procurement anti-collusion safeguards was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N32" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O32" s="5" t="str">
-        <x:v>Sourcing above defined thresholds follows a documented competitive process with sealed submissions, evaluation by a panel against pre-set criteria, conflict declarations and independent review of single-source awards.</x:v>
-      </x:c>
-      <x:c r="P32" s="5" t="str">
-        <x:v>The procurement owner must require, above defined thresholds, that evaluation criteria and weightings are fixed and recorded before submissions are opened, submissions remain sealed until a scheduled opening witnessed by at least two people, evaluation is performed by a panel with signed conflict declarations, and single-source or emergency awards require documented justification and independent approval; a periodic analysis reviews award concentration, repeated near-identical pricing and rotating winners.</x:v>
-      </x:c>
-      <x:c r="Q32" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R32" s="5" t="str">
-        <x:v>60 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="5" t="str">
-        <x:v>MF-D7-Q05</x:v>
-      </x:c>
-      <x:c r="B33" s="5" t="str">
-        <x:v>D7-Q05</x:v>
-      </x:c>
-      <x:c r="C33" s="5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="D33" s="5" t="str">
-        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E33" s="5" t="str">
-        <x:v>High-risk suppliers or third-party relationships are periodically monitored or reviewed.</x:v>
-      </x:c>
-      <x:c r="F33" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G33" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H33" s="5" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="I33" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J33" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K33" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L33" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M33" s="5" t="str">
-        <x:v>Ongoing high-risk third-party monitoring was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N33" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O33" s="5" t="str">
-        <x:v>High-risk third parties are re-screened and performance-reviewed on a risk-based cycle covering ownership change, sanctions status, delivery performance, pricing drift and spend concentration.</x:v>
-      </x:c>
-      <x:c r="P33" s="5" t="str">
-        <x:v>The vendor-risk owner must define a risk-based monitoring cycle in which high-risk third parties are re-screened for ownership and sanctions change, reviewed for delivery and quality performance, validated for pricing drift against benchmark or contract, and analysed for spend concentration and unusual growth; findings requiring action are logged with owners, and failure to complete a cycle triggers escalation to the CFO.</x:v>
-      </x:c>
-      <x:c r="Q33" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="R33" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="5" t="str">
-        <x:v>MF-D7-Q06</x:v>
-      </x:c>
-      <x:c r="B34" s="5" t="str">
-        <x:v>D7-Q06</x:v>
-      </x:c>
-      <x:c r="C34" s="5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="D34" s="5" t="str">
-        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E34" s="5" t="str">
-        <x:v>Procurement or vendor-management activity is subject to oversight or periodic review.</x:v>
-      </x:c>
-      <x:c r="F34" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G34" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H34" s="5" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="I34" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J34" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K34" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L34" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M34" s="5" t="str">
-        <x:v>Independent oversight of procurement and vendor management was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N34" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O34" s="5" t="str">
-        <x:v>An independent function periodically reviews procurement and vendor-master activity covering master-data changes, award patterns, spend outside contract and policy exceptions.</x:v>
-      </x:c>
-      <x:c r="P34" s="5" t="str">
-        <x:v>The audit committee must commission periodic independent review of procurement and vendor management covering all vendor-master creations and amendments with approver identity, award patterns by buyer and supplier, spend outside approved contracts or thresholds, use of emergency and single-source routes, and policy exception volumes by individual; findings are reported to governance with owners and due dates and tracked to closure.</x:v>
-      </x:c>
-      <x:c r="Q34" s="5" t="str">
-        <x:v>Audit Committee Chair / CFO</x:v>
-      </x:c>
-      <x:c r="R34" s="5" t="str">
-        <x:v>90 days</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="5" t="str">
-        <x:v>MF-D8-Q06</x:v>
-      </x:c>
-      <x:c r="B35" s="5" t="str">
-        <x:v>D8-Q06</x:v>
-      </x:c>
-      <x:c r="C35" s="5" t="str">
-        <x:v>D8</x:v>
-      </x:c>
-      <x:c r="D35" s="5" t="str">
-        <x:v>Digital and Identity Fraud Risk</x:v>
-      </x:c>
-      <x:c r="E35" s="5" t="str">
-        <x:v>Employees and users know how to report suspicious digital activity or account-security concerns.</x:v>
-      </x:c>
-      <x:c r="F35" s="5" t="str">
-        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
-      </x:c>
-      <x:c r="G35" s="5" t="str">
-        <x:v>cross_domain_dependency</x:v>
-      </x:c>
-      <x:c r="H35" s="5" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="I35" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="J35" s="5" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="K35" s="5" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="L35" s="5" t="str">
-        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
-      </x:c>
-      <x:c r="M35" s="5" t="str">
-        <x:v>Reporting route for suspicious digital activity was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
-      </x:c>
-      <x:c r="N35" s="5" t="str">
-        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
-      </x:c>
-      <x:c r="O35" s="5" t="str">
-        <x:v>Reporting routes are published for both staff and external users, monitored during defined hours with defined response times, and feed directly into monitoring and incident response.</x:v>
-      </x:c>
-      <x:c r="P35" s="5" t="str">
-        <x:v>The security operations owner must publish a clearly signposted route for staff and, where relevant, external users to report suspicious messages, unexpected account changes and suspected compromise, define monitored hours and target response times, connect reports directly into the alert triage and incident-response process, provide acknowledgement and outcome feedback, and track reporting volume and response time against target.</x:v>
-      </x:c>
-      <x:c r="Q35" s="5" t="str">
-        <x:v>Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="R35" s="5" t="str">
-        <x:v>60 days</x:v>
+        <x:v>Use the named evidence and effectiveness fields for follow-up.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R337f79845e854a78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7f33ddfbfd0473f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2437,6 +527,1998 @@
     <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="24" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="24" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Finding ID</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Question code</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Domain code</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Domain</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>Control statement</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>Recorded response</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>Materiality class</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Materiality score</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str">
+        <x:v>Critical control</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="str">
+        <x:v>Hard gate</x:v>
+      </x:c>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Gap classification</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="str">
+        <x:v>Selection reasons</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="str">
+        <x:v>Diagnosis</x:v>
+      </x:c>
+      <x:c r="N1" s="3" t="str">
+        <x:v>Why it matters</x:v>
+      </x:c>
+      <x:c r="O1" s="3" t="str">
+        <x:v>Expected control standard</x:v>
+      </x:c>
+      <x:c r="P1" s="3" t="str">
+        <x:v>Recommended control</x:v>
+      </x:c>
+      <x:c r="Q1" s="3" t="str">
+        <x:v>Accountable owner</x:v>
+      </x:c>
+      <x:c r="R1" s="3" t="str">
+        <x:v>Target period</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="5" t="str">
+        <x:v>MF-D1-Q04</x:v>
+      </x:c>
+      <x:c r="B2" s="5" t="str">
+        <x:v>D1-Q04</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="str">
+        <x:v>Fraud Leadership and Governance</x:v>
+      </x:c>
+      <x:c r="E2" s="5" t="str">
+        <x:v>Management owns fraud risk, while internal audit or assurance functions provide independent review where they exist.</x:v>
+      </x:c>
+      <x:c r="F2" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="str">
+        <x:v>maturity_constraint</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="n">
+        <x:v>2680</x:v>
+      </x:c>
+      <x:c r="I2" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J2" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K2" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L2" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; MATURITY_CAP_EVENT; CRITICAL_GAP; MAJOR_GAP</x:v>
+      </x:c>
+      <x:c r="M2" s="5" t="str">
+        <x:v>Management-versus-assurance role separation was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N2" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O2" s="5" t="str">
+        <x:v>Management designs and operates fraud controls; internal audit or another independent function periodically tests them and reports without assuming management responsibility.</x:v>
+      </x:c>
+      <x:c r="P2" s="5" t="str">
+        <x:v>The CEO and audit-committee chair must approve a RACI that assigns control operation to management and risk owners, reserves independent validation and unrestricted reporting for internal audit or equivalent assurance, and requires annual conflict review; the company secretary retains the approved RACI and minutes.</x:v>
+      </x:c>
+      <x:c r="Q2" s="5" t="str">
+        <x:v>CEO / Managing Director</x:v>
+      </x:c>
+      <x:c r="R2" s="5" t="str">
+        <x:v>30 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="5" t="str">
+        <x:v>MF-D3-Q03</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="str">
+        <x:v>D3-Q03</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="str">
+        <x:v>D3</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="str">
+        <x:v>Operational Fraud Controls</x:v>
+      </x:c>
+      <x:c r="E3" s="5" t="str">
+        <x:v>Supplier onboarding includes checks on business information, ownership, banking details or other fraud-risk indicators.</x:v>
+      </x:c>
+      <x:c r="F3" s="5" t="str">
+        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="n">
+        <x:v>2660</x:v>
+      </x:c>
+      <x:c r="I3" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L3" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; ABSENT_CONTROL; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M3" s="5" t="str">
+        <x:v>Supplier-onboarding verification was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N3" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O3" s="5" t="str">
+        <x:v>Every supplier is verified against legal identity, ownership, tax/banking and risk indicators before activation, with enhanced review for high-risk suppliers.</x:v>
+      </x:c>
+      <x:c r="P3" s="5" t="str">
+        <x:v>Procurement performs a pre-activation checklist across every proposed supplier, independently verifies registration and bank ownership, screens beneficial owners and conflicts, risk-rates the supplier, and blocks ERP activation until a second reviewer signs; the vendor master retains the evidence package.</x:v>
+      </x:c>
+      <x:c r="Q3" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R3" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="5" t="str">
+        <x:v>MF-D7-Q04</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="str">
+        <x:v>D7-Q04</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="str">
+        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="str">
+        <x:v>Supplier payment processes include checks to reduce invoice manipulation, fake vendors, bank-detail changes or vendor impersonation.</x:v>
+      </x:c>
+      <x:c r="F4" s="5" t="str">
+        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
+      </x:c>
+      <x:c r="G4" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="n">
+        <x:v>2660</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J4" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K4" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L4" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; ABSENT_CONTROL; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M4" s="5" t="str">
+        <x:v>Supplier payment and bank-detail-change verification was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N4" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O4" s="5" t="str">
+        <x:v>Every bank-detail change is verified independently through a trusted pre-existing contact and segregated from payment approval; invoices are matched to approved supplier and purchasing records.</x:v>
+      </x:c>
+      <x:c r="P4" s="5" t="str">
+        <x:v>Accounts Payable quarantines every bank-detail change, retrieves a contact from the pre-change vendor master, completes and records an outbound callback, obtains second-person approval from someone outside vendor-master maintenance, blocks payment until verification, and gives the CFO a monthly report of all changes, failures and bypass attempts.</x:v>
+      </x:c>
+      <x:c r="Q4" s="5" t="str">
+        <x:v>CFO</x:v>
+      </x:c>
+      <x:c r="R4" s="5" t="str">
+        <x:v>30 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="5" t="str">
+        <x:v>MF-D5-Q05</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="str">
+        <x:v>D5-Q05</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="str">
+        <x:v>D5</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="str">
+        <x:v>Fraud Incident Response</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="str">
+        <x:v>Evidence linked to suspected fraud is identified, preserved and handled appropriately.</x:v>
+      </x:c>
+      <x:c r="F5" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G5" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="n">
+        <x:v>2430</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K5" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L5" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M5" s="5" t="str">
+        <x:v>Fraud evidence preservation and chain of custody was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N5" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O5" s="5" t="str">
+        <x:v>Evidence is collected under legal direction where needed, hashed or sealed, logged through every transfer, access-restricted and retained under an approved schedule.</x:v>
+      </x:c>
+      <x:c r="P5" s="5" t="str">
+        <x:v>The investigation lead opens an evidence register for every material case; trained custodians identify sources, create forensic copies or sealed originals, record hashes/seal numbers, collector/time/location and every transfer, store evidence in access-controlled repositories, and escalate any custody break immediately to Legal.</x:v>
+      </x:c>
+      <x:c r="Q5" s="5" t="str">
+        <x:v>General Counsel / COO</x:v>
+      </x:c>
+      <x:c r="R5" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="5" t="str">
+        <x:v>MF-D1-Q01</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>D1-Q01</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="str">
+        <x:v>Fraud Leadership and Governance</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="str">
+        <x:v>A named senior owner is accountable for fraud risk management and has authority to drive action.</x:v>
+      </x:c>
+      <x:c r="F6" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G6" s="5" t="str">
+        <x:v>maturity_constraint</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="I6" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K6" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L6" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; MATURITY_CAP_EVENT; CRITICAL_GAP</x:v>
+      </x:c>
+      <x:c r="M6" s="5" t="str">
+        <x:v>Senior fraud-risk ownership was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N6" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O6" s="5" t="str">
+        <x:v>A named senior executive owns the fraud-risk programme, its budget, unresolved exceptions and reporting to the governing body.</x:v>
+      </x:c>
+      <x:c r="P6" s="5" t="str">
+        <x:v>The CEO must issue a dated fraud-risk accountability mandate naming one executive, delegated decision rights, budget authority, quarterly reporting obligations and a 30-day escalation route for overdue control actions; the company secretary retains approvals and quarterly packs.</x:v>
+      </x:c>
+      <x:c r="Q6" s="5" t="str">
+        <x:v>CEO / Managing Director</x:v>
+      </x:c>
+      <x:c r="R6" s="5" t="str">
+        <x:v>30 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="5" t="str">
+        <x:v>MF-D4-Q01</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>D4-Q01</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
+        <x:v>Fraud Detection Capability</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="str">
+        <x:v>The organisation monitors transactions or operational activity for unusual patterns, anomalies or red flags.</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="n">
+        <x:v>2300</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J7" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K7" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L7" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M7" s="5" t="str">
+        <x:v>Transaction and activity monitoring was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N7" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O7" s="5" t="str">
+        <x:v>Defined monitoring covers the material transaction and activity population, uses risk-based indicators, and produces reviewable output on a set rhythm rather than relying on incidental discovery.</x:v>
+      </x:c>
+      <x:c r="P7" s="5" t="str">
+        <x:v>The monitoring owner must define red-flag indicators per material process — duplicate payments, round-value patterns, out-of-hours activity, unusual volume by user, adjustments reversing prior entries, and supplier or customer concentration — run them against the complete transaction population on a set rhythm, and route output into the exception queue with named reviewers and SLAs; coverage against the process fraud maps is reported to the fraud forum.</x:v>
+      </x:c>
+      <x:c r="Q7" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R7" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="5" t="str">
+        <x:v>MF-D8-Q01</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>D8-Q01</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="str">
+        <x:v>D8</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
+        <x:v>Digital and Identity Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="str">
+        <x:v>The organisation verifies the identity of customers, users, employees, suppliers or counterparties where identity misuse could create fraud loss or harm.</x:v>
+      </x:c>
+      <x:c r="F8" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G8" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="n">
+        <x:v>2300</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J8" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K8" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L8" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M8" s="5" t="str">
+        <x:v>Identity verification at risk points was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N8" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O8" s="5" t="str">
+        <x:v>Identity verification is applied at defined risk points using independent sources proportionate to risk, with results recorded, exceptions approved and re-verification on sensitive change.</x:v>
+      </x:c>
+      <x:c r="P8" s="5" t="str">
+        <x:v>The process owner must define the risk points requiring verification — customer or beneficiary enrolment, employee onboarding, supplier activation and counterparty contracting — and apply proportionate checks against independent sources such as identity documents validated for authenticity, company registration records, and confirmation of contact details through independently obtained channels; results and evidence are retained under applicable data-protection obligations, exceptions require documented approval, and sensitive profile or banking changes trigger re-verification.</x:v>
+      </x:c>
+      <x:c r="Q8" s="5" t="str">
+        <x:v>COO / CFO</x:v>
+      </x:c>
+      <x:c r="R8" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="5" t="str">
+        <x:v>MF-D10-Q01</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="str">
+        <x:v>D10-Q01</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="str">
+        <x:v>D10</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="str">
+        <x:v>Continuous Improvement and Fraud Risk Monitoring</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="str">
+        <x:v>The organisation periodically reviews its fraud risks and control environment.</x:v>
+      </x:c>
+      <x:c r="F9" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="n">
+        <x:v>2220</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J9" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K9" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L9" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP</x:v>
+      </x:c>
+      <x:c r="M9" s="5" t="str">
+        <x:v>Periodic fraud risk and control environment review was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N9" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O9" s="5" t="str">
+        <x:v>A scheduled review reassesses fraud risks, tests whether key controls still operate as designed, and reports a consolidated position with owned actions to governance.</x:v>
+      </x:c>
+      <x:c r="P9" s="5" t="str">
+        <x:v>The Head of Risk must run a scheduled review that revisits the fraud risk assessment for continued relevance, confirms for each key control that it still has a named owner and is still operating by sampling recent evidence rather than accepting attestation, records any control that has lapsed or degraded, and reports a consolidated risk and control position to the governing body with owned remediation actions and due dates.</x:v>
+      </x:c>
+      <x:c r="Q9" s="5" t="str">
+        <x:v>CEO / Managing Director</x:v>
+      </x:c>
+      <x:c r="R9" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="5" t="str">
+        <x:v>MF-D2-Q01</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="str">
+        <x:v>D2-Q01</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="str">
+        <x:v>Fraud Risk Identification</x:v>
+      </x:c>
+      <x:c r="E10" s="5" t="str">
+        <x:v>The organisation has completed a structured fraud risk assessment within the past two years.</x:v>
+      </x:c>
+      <x:c r="F10" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="n">
+        <x:v>2220</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J10" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K10" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L10" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; MAJOR_GAP</x:v>
+      </x:c>
+      <x:c r="M10" s="5" t="str">
+        <x:v>Structured fraud risk assessment currency was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N10" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O10" s="5" t="str">
+        <x:v>A structured fraud risk assessment completed within the past two years covers the material processes, uses a repeatable method, rates inherent and residual risk, names owners and produces a tracked treatment plan.</x:v>
+      </x:c>
+      <x:c r="P10" s="5" t="str">
+        <x:v>The Head of Risk must run a documented fraud risk assessment at least every two years using a repeatable method: scope the material processes and channels, identify fraud scenarios per process with the roles able to execute them, rate likelihood and impact before and after existing controls, name a treatment owner and due date for every unacceptable residual risk, and obtain governing-body approval of the plan; assessment date, participants and method are retained.</x:v>
+      </x:c>
+      <x:c r="Q10" s="5" t="str">
+        <x:v>CEO / Managing Director</x:v>
+      </x:c>
+      <x:c r="R10" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="5" t="str">
+        <x:v>MF-D3-Q04</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>D3-Q04</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>D3</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
+        <x:v>Operational Fraud Controls</x:v>
+      </x:c>
+      <x:c r="E11" s="5" t="str">
+        <x:v>System and data access are granted based on role requirements and reviewed periodically.</x:v>
+      </x:c>
+      <x:c r="F11" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G11" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="n">
+        <x:v>2150</x:v>
+      </x:c>
+      <x:c r="I11" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J11" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K11" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L11" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M11" s="5" t="str">
+        <x:v>Role-based user-access governance was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N11" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O11" s="5" t="str">
+        <x:v>All in-scope user access maps to an approved role, is reviewed by the business owner each quarter and is removed promptly after role change or exit.</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="str">
+        <x:v>System owners export the complete active-user population quarterly; line managers compare every entitlement to the approved role matrix, record keep/remove decisions, and route exceptions to IT for closure within 10 business days; Risk samples completed reviews and overdue removals are escalated to the COO.</x:v>
+      </x:c>
+      <x:c r="Q11" s="5" t="str">
+        <x:v>COO</x:v>
+      </x:c>
+      <x:c r="R11" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="5" t="str">
+        <x:v>MF-D5-Q01</x:v>
+      </x:c>
+      <x:c r="B12" s="5" t="str">
+        <x:v>D5-Q01</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="str">
+        <x:v>D5</x:v>
+      </x:c>
+      <x:c r="D12" s="5" t="str">
+        <x:v>Fraud Incident Response</x:v>
+      </x:c>
+      <x:c r="E12" s="5" t="str">
+        <x:v>The organisation has a documented process for responding to suspected fraud incidents.</x:v>
+      </x:c>
+      <x:c r="F12" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G12" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="n">
+        <x:v>2150</x:v>
+      </x:c>
+      <x:c r="I12" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J12" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K12" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L12" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M12" s="5" t="str">
+        <x:v>Fraud incident-response governance was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N12" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O12" s="5" t="str">
+        <x:v>A documented plan defines intake, severity, command roles, containment, legal/evidence decisions, communications and closure, and is rehearsed annually.</x:v>
+      </x:c>
+      <x:c r="P12" s="5" t="str">
+        <x:v>The incident-response lead maintains a version-controlled plan covering every reported fraud incident, names an incident commander and deputies, classifies severity at intake, convenes Legal/HR/IT/Finance roles, records decisions and containment actions, and runs an annual tabletop with tracked remediation.</x:v>
+      </x:c>
+      <x:c r="Q12" s="5" t="str">
+        <x:v>COO / General Counsel</x:v>
+      </x:c>
+      <x:c r="R12" s="5" t="str">
+        <x:v>30 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="5" t="str">
+        <x:v>MF-D8-Q02</x:v>
+      </x:c>
+      <x:c r="B13" s="5" t="str">
+        <x:v>D8-Q02</x:v>
+      </x:c>
+      <x:c r="C13" s="5" t="str">
+        <x:v>D8</x:v>
+      </x:c>
+      <x:c r="D13" s="5" t="str">
+        <x:v>Digital and Identity Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E13" s="5" t="str">
+        <x:v>Systems or digital platforms are monitored for suspicious activity such as unusual login, access, profile, transaction or account behaviour.</x:v>
+      </x:c>
+      <x:c r="F13" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G13" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="n">
+        <x:v>2150</x:v>
+      </x:c>
+      <x:c r="I13" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J13" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K13" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L13" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M13" s="5" t="str">
+        <x:v>Suspicious digital-activity monitoring was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N13" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O13" s="5" t="str">
+        <x:v>Risk-based monitoring covers material digital events, alerts are triaged to defined SLAs and rules are tuned from confirmed outcomes.</x:v>
+      </x:c>
+      <x:c r="P13" s="5" t="str">
+        <x:v>The security monitoring owner inventories material login, privilege, profile and transaction events, implements risk rules across the full in-scope event feed, assigns alerts to trained analysts, preserves dispositions and escalates high-risk account compromise immediately; monthly tuning uses confirmed true/false positives.</x:v>
+      </x:c>
+      <x:c r="Q13" s="5" t="str">
+        <x:v>Chief Technology Officer</x:v>
+      </x:c>
+      <x:c r="R13" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="5" t="str">
+        <x:v>MF-D8-Q04</x:v>
+      </x:c>
+      <x:c r="B14" s="5" t="str">
+        <x:v>D8-Q04</x:v>
+      </x:c>
+      <x:c r="C14" s="5" t="str">
+        <x:v>D8</x:v>
+      </x:c>
+      <x:c r="D14" s="5" t="str">
+        <x:v>Digital and Identity Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E14" s="5" t="str">
+        <x:v>Access to sensitive digital systems, administrator rights and confidential data is restricted and reviewed.</x:v>
+      </x:c>
+      <x:c r="F14" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G14" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H14" s="5" t="n">
+        <x:v>2150</x:v>
+      </x:c>
+      <x:c r="I14" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J14" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K14" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L14" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M14" s="5" t="str">
+        <x:v>Privileged and administrator access governance was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N14" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O14" s="5" t="str">
+        <x:v>Every privileged account is named, justified, least-privileged, strongly authenticated, logged and independently recertified quarterly; emergency access expires automatically.</x:v>
+      </x:c>
+      <x:c r="P14" s="5" t="str">
+        <x:v>IT Security maintains a complete privileged-account register, links each human and service account to an owner and approved justification, enforces separate named admin identities and MFA, records privileged sessions, and sends the full population quarterly to system owners and Risk for independent keep/remove certification; removals close within 24 hours for leavers and five business days otherwise.</x:v>
+      </x:c>
+      <x:c r="Q14" s="5" t="str">
+        <x:v>Chief Technology Officer</x:v>
+      </x:c>
+      <x:c r="R14" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="5" t="str">
+        <x:v>MF-D4-Q03</x:v>
+      </x:c>
+      <x:c r="B15" s="5" t="str">
+        <x:v>D4-Q03</x:v>
+      </x:c>
+      <x:c r="C15" s="5" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="D15" s="5" t="str">
+        <x:v>Fraud Detection Capability</x:v>
+      </x:c>
+      <x:c r="E15" s="5" t="str">
+        <x:v>Analytics, rules, reports or data checks are used to identify suspicious transactions, behaviour or control exceptions.</x:v>
+      </x:c>
+      <x:c r="F15" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G15" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="I15" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J15" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K15" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L15" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M15" s="5" t="str">
+        <x:v>Analytics and rule-based detection was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N15" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O15" s="5" t="str">
+        <x:v>A maintained catalogue of rules and data checks maps each validate to a fraud scenario, runs against reconciled data, and is tuned from confirmed outcomes.</x:v>
+      </x:c>
+      <x:c r="P15" s="5" t="str">
+        <x:v>The monitoring owner must maintain a rule catalogue in which every validate names the fraud scenario it addresses, the data source, the threshold and the reviewing role; tests include duplicate and near-duplicate payments, supplier and employee bank-detail or address matches, unusual approval pairings, dormant-account reactivation and threshold-adjacent transaction clustering; results reconcile to source control totals and rules are tuned monthly from confirmed true and false positives.</x:v>
+      </x:c>
+      <x:c r="Q15" s="5" t="str">
+        <x:v>CFO / Chief Technology Officer</x:v>
+      </x:c>
+      <x:c r="R15" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="5" t="str">
+        <x:v>MF-D8-Q08</x:v>
+      </x:c>
+      <x:c r="B16" s="5" t="str">
+        <x:v>D8-Q08</x:v>
+      </x:c>
+      <x:c r="C16" s="5" t="str">
+        <x:v>D8</x:v>
+      </x:c>
+      <x:c r="D16" s="5" t="str">
+        <x:v>Digital and Identity Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="str">
+        <x:v>The organisation can detect or investigate identity misuse, account takeover, impersonation or unauthorised profile changes where relevant.</x:v>
+      </x:c>
+      <x:c r="F16" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G16" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="I16" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J16" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K16" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L16" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M16" s="5" t="str">
+        <x:v>Identity misuse detection and investigation capability was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N16" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O16" s="5" t="str">
+        <x:v>Sufficient logging, alerting and investigative capability exists to identify compromise, reconstruct what occurred, contain it and support recovery or referral.</x:v>
+      </x:c>
+      <x:c r="P16" s="5" t="str">
+        <x:v>The security operations owner must ensure authentication events, credential and multi-factor changes, profile and banking-detail changes, device and session identifiers and transaction history are logged for all material identity-bearing systems and retained for a defined period consistent with data-protection obligations; alerting covers impossible-travel and anomalous login, credential and contact-detail change followed by transaction, and dormant-account reactivation, with an investigation runbook defining containment such as session revocation and forced credential reset.</x:v>
+      </x:c>
+      <x:c r="Q16" s="5" t="str">
+        <x:v>Chief Technology Officer</x:v>
+      </x:c>
+      <x:c r="R16" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="5" t="str">
+        <x:v>MF-D2-Q02</x:v>
+      </x:c>
+      <x:c r="B17" s="5" t="str">
+        <x:v>D2-Q02</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="D17" s="5" t="str">
+        <x:v>Fraud Risk Identification</x:v>
+      </x:c>
+      <x:c r="E17" s="5" t="str">
+        <x:v>Fraud risks have been mapped across important processes such as procurement, payments, refunds, claims, stock, supplier management or service delivery.</x:v>
+      </x:c>
+      <x:c r="F17" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G17" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H17" s="5" t="n">
+        <x:v>1940</x:v>
+      </x:c>
+      <x:c r="I17" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J17" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="K17" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L17" s="5" t="str">
+        <x:v>HARD_GATE_FAILURE; CRITICAL_CONTROL_FAILURE; CRITICAL_GAP</x:v>
+      </x:c>
+      <x:c r="M17" s="5" t="str">
+        <x:v>Process-level fraud risk mapping was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N17" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology hard gate and must be remediated before relying on the aggregate maturity result.</x:v>
+      </x:c>
+      <x:c r="O17" s="5" t="str">
+        <x:v>Each material process — procurement, payments, refunds, claims, stock, supplier management and service delivery as applicable — has documented fraud scenarios, the roles able to execute them, and the controls relied upon.</x:v>
+      </x:c>
+      <x:c r="P17" s="5" t="str">
+        <x:v>The Head of Risk must produce a process-by-process fraud map covering every material value-bearing process: for each, record the fraud scenarios, the roles and system permissions able to execute them alone or in collusion, the preventive and detective controls relied upon, and the residual gap; process owners sign their own map, and any process without a mapped control owner escalates to the fraud-risk executive.</x:v>
+      </x:c>
+      <x:c r="Q17" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R17" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="5" t="str">
+        <x:v>MF-D7-Q01</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="str">
+        <x:v>D7-Q01</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="D18" s="5" t="str">
+        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E18" s="5" t="str">
+        <x:v>Suppliers, contractors or other third parties are subject to due diligence before being engaged.</x:v>
+      </x:c>
+      <x:c r="F18" s="5" t="str">
+        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
+      </x:c>
+      <x:c r="G18" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H18" s="5" t="n">
+        <x:v>1480</x:v>
+      </x:c>
+      <x:c r="I18" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J18" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K18" s="5" t="str">
+        <x:v>critical</x:v>
+      </x:c>
+      <x:c r="L18" s="5" t="str">
+        <x:v>CRITICAL_CONTROL_FAILURE; CRITICAL_GAP; ABSENT_CONTROL; WEAKEST_DOMAIN; CROSS_DOMAIN_DEPENDENCY; PRIORITY_SCENARIO_ENABLER</x:v>
+      </x:c>
+      <x:c r="M18" s="5" t="str">
+        <x:v>Third-party pre-engagement due diligence was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N18" s="5" t="str">
+        <x:v>This recorded weakness affects a methodology critical control and warrants priority treatment.</x:v>
+      </x:c>
+      <x:c r="O18" s="5" t="str">
+        <x:v>All third parties receive proportionate identity, ownership, sanctions/conflict and capability checks before contracting, with enhanced approval for high-risk relationships.</x:v>
+      </x:c>
+      <x:c r="P18" s="5" t="str">
+        <x:v>The vendor-risk owner risk-rates every proposed third party, verifies legal identity and beneficial ownership from independent sources, screens sanctions/adverse and employee conflicts, documents capability and bank ownership, and requires Compliance approval for high-risk cases before contract signature or system activation.</x:v>
+      </x:c>
+      <x:c r="Q18" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R18" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="5" t="str">
+        <x:v>MF-D4-Q02</x:v>
+      </x:c>
+      <x:c r="B19" s="5" t="str">
+        <x:v>D4-Q02</x:v>
+      </x:c>
+      <x:c r="C19" s="5" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="D19" s="5" t="str">
+        <x:v>Fraud Detection Capability</x:v>
+      </x:c>
+      <x:c r="E19" s="5" t="str">
+        <x:v>Exception reports or alerts highlighting unusual transactions or activities are generated and reviewed regularly.</x:v>
+      </x:c>
+      <x:c r="F19" s="5" t="str">
+        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
+      </x:c>
+      <x:c r="G19" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H19" s="5" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="I19" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J19" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K19" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L19" s="5" t="str">
+        <x:v>ABSENT_CONTROL; WEAKEST_DOMAIN; CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M19" s="5" t="str">
+        <x:v>Exception-report review was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N19" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O19" s="5" t="str">
+        <x:v>The complete alert population is assigned, triaged to risk-based SLAs, dispositioned with evidence and independently reviewed for ageing and quality.</x:v>
+      </x:c>
+      <x:c r="P19" s="5" t="str">
+        <x:v>The monitoring owner generates a complete daily or weekly exception queue, assigns each alert to a trained reviewer, records investigation evidence and disposition, and escalates high-risk alerts immediately and all overdue alerts weekly; Risk performs a monthly closure-quality sample.</x:v>
+      </x:c>
+      <x:c r="Q19" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R19" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="5" t="str">
+        <x:v>MF-D10-Q04</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="str">
+        <x:v>D10-Q04</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="str">
+        <x:v>D10</x:v>
+      </x:c>
+      <x:c r="D20" s="5" t="str">
+        <x:v>Continuous Improvement and Fraud Risk Monitoring</x:v>
+      </x:c>
+      <x:c r="E20" s="5" t="str">
+        <x:v>The organisation monitors fraud trends affecting its sector, geography, customer environment or supplier base.</x:v>
+      </x:c>
+      <x:c r="F20" s="5" t="str">
+        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
+      </x:c>
+      <x:c r="G20" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H20" s="5" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="I20" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J20" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K20" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L20" s="5" t="str">
+        <x:v>ABSENT_CONTROL; WEAKEST_DOMAIN</x:v>
+      </x:c>
+      <x:c r="M20" s="5" t="str">
+        <x:v>Fraud trend monitoring across sector and environment was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N20" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O20" s="5" t="str">
+        <x:v>External trend monitoring is assigned, run on a defined rhythm, compared against internal loss and incident patterns, and reported with implications for control priorities.</x:v>
+      </x:c>
+      <x:c r="P20" s="5" t="str">
+        <x:v>The Head of Risk must assign trend monitoring across the sector, operating geographies, customer environment and supplier base using industry, insurer, law-enforcement and peer sources, compare external trends against the organisation’s own incident and loss data to identify both matches and gaps, and report each cycle with an explicit implication for control priorities and the treatment plan.</x:v>
+      </x:c>
+      <x:c r="Q20" s="5" t="str">
+        <x:v>Head of Risk</x:v>
+      </x:c>
+      <x:c r="R20" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="5" t="str">
+        <x:v>MF-D4-Q06</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="str">
+        <x:v>D4-Q06</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="D21" s="5" t="str">
+        <x:v>Fraud Detection Capability</x:v>
+      </x:c>
+      <x:c r="E21" s="5" t="str">
+        <x:v>People responsible for monitoring suspicious activity know when to escalate concerns and have authority to do so.</x:v>
+      </x:c>
+      <x:c r="F21" s="5" t="str">
+        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
+      </x:c>
+      <x:c r="G21" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H21" s="5" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="I21" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J21" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K21" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L21" s="5" t="str">
+        <x:v>ABSENT_CONTROL; CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M21" s="5" t="str">
+        <x:v>Escalation authority for monitoring staff was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N21" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O21" s="5" t="str">
+        <x:v>Written escalation criteria, routes and timeframes are defined, staff are trained on them, and escalation can bypass any implicated line manager.</x:v>
+      </x:c>
+      <x:c r="P21" s="5" t="str">
+        <x:v>The Head of Risk must publish escalation criteria defining what must be escalated, to whom and within what time, grant monitoring staff explicit authority to escalate directly to the fraud-risk executive or audit-committee chair where a manager is implicated, protect escalators from retaliation, train the monitoring team annually, and review escalation timeliness against criteria each quarter.</x:v>
+      </x:c>
+      <x:c r="Q21" s="5" t="str">
+        <x:v>Head of Risk</x:v>
+      </x:c>
+      <x:c r="R21" s="5" t="str">
+        <x:v>30 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="5" t="str">
+        <x:v>MF-D2-Q06</x:v>
+      </x:c>
+      <x:c r="B22" s="5" t="str">
+        <x:v>D2-Q06</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="D22" s="5" t="str">
+        <x:v>Fraud Risk Identification</x:v>
+      </x:c>
+      <x:c r="E22" s="5" t="str">
+        <x:v>The organisation monitors emerging fraud threats affecting its industry, geography or operating environment.</x:v>
+      </x:c>
+      <x:c r="F22" s="5" t="str">
+        <x:v>Not in place — The control, process or capability does not exist or is not recognised as required.</x:v>
+      </x:c>
+      <x:c r="G22" s="5" t="str">
+        <x:v>control_failure</x:v>
+      </x:c>
+      <x:c r="H22" s="5" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="I22" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J22" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K22" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L22" s="5" t="str">
+        <x:v>ABSENT_CONTROL</x:v>
+      </x:c>
+      <x:c r="M22" s="5" t="str">
+        <x:v>Emerging fraud-threat monitoring was self-assessed as "Not in place" (The control, process or capability does not exist or is not recognised as required; normalised score 0/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N22" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O22" s="5" t="str">
+        <x:v>Named sources are monitored on a defined rhythm, relevance is assessed against the organisation’s processes and channels, and material threats generate a control review or an explicit accept decision.</x:v>
+      </x:c>
+      <x:c r="P22" s="5" t="str">
+        <x:v>The Head of Risk must assign responsibility for monitoring a named source set covering industry associations, insurer and broker briefings, regional law-enforcement and regulator advisories, peer and supplier incident reports and relevant local crime patterns; each cycle threats are logged, assessed for relevance to the organisation’s processes, channels and geographies, and either raised as a control review with an owner or recorded as an explicit accept decision with rationale.</x:v>
+      </x:c>
+      <x:c r="Q22" s="5" t="str">
+        <x:v>Head of Risk</x:v>
+      </x:c>
+      <x:c r="R22" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="5" t="str">
+        <x:v>MF-D4-Q04</x:v>
+      </x:c>
+      <x:c r="B23" s="5" t="str">
+        <x:v>D4-Q04</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="D23" s="5" t="str">
+        <x:v>Fraud Detection Capability</x:v>
+      </x:c>
+      <x:c r="E23" s="5" t="str">
+        <x:v>Detection controls are updated when new fraud risks, fraud methods or operational changes emerge.</x:v>
+      </x:c>
+      <x:c r="F23" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G23" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H23" s="5" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I23" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J23" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K23" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L23" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M23" s="5" t="str">
+        <x:v>Detection control currency was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N23" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O23" s="5" t="str">
+        <x:v>Defined triggers require detection rules and indicators to be reassessed, with changes recorded, validated before deployment and reported to the fraud forum.</x:v>
+      </x:c>
+      <x:c r="P23" s="5" t="str">
+        <x:v>The monitoring owner must reassess the detection set whenever a new fraud method is identified internally or externally, a material process or system changes, or a confirmed incident bypassed existing detection; each change is documented with rationale, validated against historical data before deployment, version-controlled, and reported with before-and-after coverage to the fraud forum.</x:v>
+      </x:c>
+      <x:c r="Q23" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R23" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="5" t="str">
+        <x:v>MF-D4-Q05</x:v>
+      </x:c>
+      <x:c r="B24" s="5" t="str">
+        <x:v>D4-Q05</x:v>
+      </x:c>
+      <x:c r="C24" s="5" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="D24" s="5" t="str">
+        <x:v>Fraud Detection Capability</x:v>
+      </x:c>
+      <x:c r="E24" s="5" t="str">
+        <x:v>Monitoring covers both internal misuse and external fraud threats where these are relevant to the organisation.</x:v>
+      </x:c>
+      <x:c r="F24" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G24" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H24" s="5" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I24" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J24" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K24" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L24" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M24" s="5" t="str">
+        <x:v>Internal and external threat monitoring coverage was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N24" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O24" s="5" t="str">
+        <x:v>Monitoring explicitly addresses employee and insider misuse alongside external attack, with indicators, data sources and reviewers defined for both.</x:v>
+      </x:c>
+      <x:c r="P24" s="5" t="str">
+        <x:v>The monitoring owner must maintain a coverage matrix showing, for each material process, the indicators addressing internal misuse — override use, permission changes, adjustments by approvers, out-of-hours access — and those addressing external threats such as supplier impersonation, customer identity misuse and channel abuse; gaps in either column are logged with an owner, and coverage is reported to the fraud forum each cycle.</x:v>
+      </x:c>
+      <x:c r="Q24" s="5" t="str">
+        <x:v>CFO / Chief Technology Officer</x:v>
+      </x:c>
+      <x:c r="R24" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="5" t="str">
+        <x:v>MF-D5-Q02</x:v>
+      </x:c>
+      <x:c r="B25" s="5" t="str">
+        <x:v>D5-Q02</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="str">
+        <x:v>D5</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="str">
+        <x:v>Fraud Incident Response</x:v>
+      </x:c>
+      <x:c r="E25" s="5" t="str">
+        <x:v>Employees know where and how to report suspected fraud or misconduct.</x:v>
+      </x:c>
+      <x:c r="F25" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G25" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H25" s="5" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I25" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J25" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K25" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L25" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M25" s="5" t="str">
+        <x:v>Workforce awareness of fraud reporting routes was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N25" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O25" s="5" t="str">
+        <x:v>Reporting routes are published in plain language, reach the entire workforce including non-desk and contract staff, and awareness is periodically validated rather than assumed.</x:v>
+      </x:c>
+      <x:c r="P25" s="5" t="str">
+        <x:v>The ethics owner must publish reporting routes in plain language across the channels the workforce actually uses — induction packs, payslip inserts, notice boards at depots and sites, intranet and supervisor briefings — covering line manager, confidential channel and conflict-free alternate route; awareness is validated periodically by short survey or spot check, and results below threshold trigger a targeted re-communication for the affected sites or teams.</x:v>
+      </x:c>
+      <x:c r="Q25" s="5" t="str">
+        <x:v>Chief People Officer / COO</x:v>
+      </x:c>
+      <x:c r="R25" s="5" t="str">
+        <x:v>30 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="5" t="str">
+        <x:v>MF-D7-Q03</x:v>
+      </x:c>
+      <x:c r="B26" s="5" t="str">
+        <x:v>D7-Q03</x:v>
+      </x:c>
+      <x:c r="C26" s="5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="D26" s="5" t="str">
+        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E26" s="5" t="str">
+        <x:v>Employees are required to disclose and manage conflicts of interest involving suppliers or third parties.</x:v>
+      </x:c>
+      <x:c r="F26" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G26" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H26" s="5" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I26" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J26" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K26" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L26" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M26" s="5" t="str">
+        <x:v>Conflict of interest declaration and management was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N26" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O26" s="5" t="str">
+        <x:v>Declarations are collected from all staff able to influence supplier selection or payment, refreshed periodically and on change, validated against supplier data, and each declared conflict carries a documented management action.</x:v>
+      </x:c>
+      <x:c r="P26" s="5" t="str">
+        <x:v>The compliance owner must require annual and on-change declarations from every employee able to influence supplier selection, contracting, receipting or payment, covering directorships, shareholdings, family relationships and outside interests; declarations are validated against the vendor master for matching surnames, addresses, contact details and bank accounts, and every declared or detected conflict receives a documented management action such as recusal, reassignment or enhanced review, recorded in a conflict register.</x:v>
+      </x:c>
+      <x:c r="Q26" s="5" t="str">
+        <x:v>CFO / General Counsel</x:v>
+      </x:c>
+      <x:c r="R26" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="5" t="str">
+        <x:v>MF-D7-Q07</x:v>
+      </x:c>
+      <x:c r="B27" s="5" t="str">
+        <x:v>D7-Q07</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="str">
+        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E27" s="5" t="str">
+        <x:v>Fraud risks are considered when using agents, brokers, distributors, intermediaries, partners or outsourced service providers where relevant.</x:v>
+      </x:c>
+      <x:c r="F27" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G27" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H27" s="5" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I27" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J27" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K27" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L27" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M27" s="5" t="str">
+        <x:v>Intermediary and outsourced provider fraud oversight was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N27" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O27" s="5" t="str">
+        <x:v>Intermediary and outsourced arrangements carry contractual fraud-control obligations, audit and information rights, defined oversight of delegated authority, and periodic assurance over the provider’s own controls.</x:v>
+      </x:c>
+      <x:c r="P27" s="5" t="str">
+        <x:v>The relationship owner must ensure every intermediary or outsourced arrangement defines in contract the fraud-control obligations, the limits of delegated authority, the right to audit and obtain records, incident-notification duties and consequences for breach; oversight includes reconciliation of transactions and collections handled on the organisation’s behalf, periodic assurance over the provider’s relevant controls, and review of any sub-contracting before it occurs.</x:v>
+      </x:c>
+      <x:c r="Q27" s="5" t="str">
+        <x:v>COO / CFO</x:v>
+      </x:c>
+      <x:c r="R27" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="5" t="str">
+        <x:v>MF-D8-Q03</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>D8-Q03</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>D8</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str">
+        <x:v>Digital and Identity Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E28" s="5" t="str">
+        <x:v>Employees receive training on phishing, social engineering and digital impersonation attempts.</x:v>
+      </x:c>
+      <x:c r="F28" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G28" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H28" s="5" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I28" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J28" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K28" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L28" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M28" s="5" t="str">
+        <x:v>Phishing and social-engineering awareness was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N28" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O28" s="5" t="str">
+        <x:v>Training is role-relevant, reinforced by periodic simulations, measured by behaviour rather than completion alone, and supported by a fast reporting route with feedback.</x:v>
+      </x:c>
+      <x:c r="P28" s="5" t="str">
+        <x:v>The security awareness owner must deliver role-relevant training covering payment-instruction and bank-detail-change requests, executive impersonation, urgency and secrecy pressure, credential-harvesting pages and voice or messaging impersonation; reinforce with periodic simulations targeted at high-risk roles such as finance and procurement, measure report rate as well as click rate, provide a one-click reporting route with feedback, and require verification through an independently obtained channel for any payment or bank-detail instruction.</x:v>
+      </x:c>
+      <x:c r="Q28" s="5" t="str">
+        <x:v>Chief Technology Officer / Chief People Officer</x:v>
+      </x:c>
+      <x:c r="R28" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="5" t="str">
+        <x:v>MF-D8-Q07</x:v>
+      </x:c>
+      <x:c r="B29" s="5" t="str">
+        <x:v>D8-Q07</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>D8</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str">
+        <x:v>Digital and Identity Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E29" s="5" t="str">
+        <x:v>Emerging digital fraud risks relevant to the organisation's operations or sector are reviewed periodically.</x:v>
+      </x:c>
+      <x:c r="F29" s="5" t="str">
+        <x:v>Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable.</x:v>
+      </x:c>
+      <x:c r="G29" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H29" s="5" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I29" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J29" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K29" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L29" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M29" s="5" t="str">
+        <x:v>Emerging digital fraud risk review was self-assessed as "Initial / ad hoc" (Some activity may occur informally or reactively, but it is not defined, owned or reliable; normalised score 20/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N29" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O29" s="5" t="str">
+        <x:v>Digital threat review runs on a defined cycle covering channel-specific attack methods, assesses them against current controls, and produces owned actions or explicit accept decisions.</x:v>
+      </x:c>
+      <x:c r="P29" s="5" t="str">
+        <x:v>The information security and digital owners must jointly run a periodic review of emerging digital fraud methods relevant to the organisation’s channels, drawing on vendor and industry advisories, incident experience and peer reporting; each method is assessed against current preventive and detective controls, gaps become owned actions with due dates, and accepted risks are recorded with rationale and reported to the risk forum.</x:v>
+      </x:c>
+      <x:c r="Q29" s="5" t="str">
+        <x:v>Chief Technology Officer</x:v>
+      </x:c>
+      <x:c r="R29" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="5" t="str">
+        <x:v>MF-D4-Q07</x:v>
+      </x:c>
+      <x:c r="B30" s="5" t="str">
+        <x:v>D4-Q07</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str">
+        <x:v>Fraud Detection Capability</x:v>
+      </x:c>
+      <x:c r="E30" s="5" t="str">
+        <x:v>Detection controls are periodically reviewed for effectiveness by management, risk, audit or another independent reviewer.</x:v>
+      </x:c>
+      <x:c r="F30" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G30" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H30" s="5" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I30" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J30" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K30" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L30" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M30" s="5" t="str">
+        <x:v>Independent review of detection effectiveness was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N30" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O30" s="5" t="str">
+        <x:v>A reviewer independent of the monitoring team periodically evaluates detection coverage, output quality and closure integrity, and reports findings to governance.</x:v>
+      </x:c>
+      <x:c r="P30" s="5" t="str">
+        <x:v>The audit committee must commission a periodic independent evaluation of detection effectiveness covering coverage against the process fraud maps, data completeness, sample retesting of closed alerts for closure quality, and detection of deliberately seeded validate conditions where practical; findings are reported to governance with owners and due dates, and remediation is tracked to closure.</x:v>
+      </x:c>
+      <x:c r="Q30" s="5" t="str">
+        <x:v>Audit Committee Chair</x:v>
+      </x:c>
+      <x:c r="R30" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="5" t="str">
+        <x:v>MF-D5-Q04</x:v>
+      </x:c>
+      <x:c r="B31" s="5" t="str">
+        <x:v>D5-Q04</x:v>
+      </x:c>
+      <x:c r="C31" s="5" t="str">
+        <x:v>D5</x:v>
+      </x:c>
+      <x:c r="D31" s="5" t="str">
+        <x:v>Fraud Incident Response</x:v>
+      </x:c>
+      <x:c r="E31" s="5" t="str">
+        <x:v>Fraud investigations follow procedures that protect confidentiality, fairness, evidence and documentation.</x:v>
+      </x:c>
+      <x:c r="F31" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G31" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H31" s="5" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I31" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J31" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K31" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L31" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M31" s="5" t="str">
+        <x:v>Investigation procedure and fairness was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N31" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O31" s="5" t="str">
+        <x:v>Written investigation procedures govern confidentiality, subject fairness, interview conduct, documentation standards and legal privilege considerations, and investigators are competent to apply them.</x:v>
+      </x:c>
+      <x:c r="P31" s="5" t="str">
+        <x:v>The investigation lead must maintain written procedures covering need-to-know confidentiality and case access restriction, the subject’s right to respond at the appropriate stage, interview conduct and record standards, contemporaneous documentation with dated file notes, retention and legal-privilege handling in consultation with Legal, and use of competent or accredited investigators; case files are quality-reviewed at closure against the procedure.</x:v>
+      </x:c>
+      <x:c r="Q31" s="5" t="str">
+        <x:v>General Counsel / COO</x:v>
+      </x:c>
+      <x:c r="R31" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="5" t="str">
+        <x:v>MF-D7-Q02</x:v>
+      </x:c>
+      <x:c r="B32" s="5" t="str">
+        <x:v>D7-Q02</x:v>
+      </x:c>
+      <x:c r="C32" s="5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="str">
+        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E32" s="5" t="str">
+        <x:v>Procurement processes include safeguards against collusion, manipulation, bid rigging or favouritism.</x:v>
+      </x:c>
+      <x:c r="F32" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G32" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H32" s="5" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I32" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J32" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K32" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L32" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M32" s="5" t="str">
+        <x:v>Procurement anti-collusion safeguards was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N32" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O32" s="5" t="str">
+        <x:v>Sourcing above defined thresholds follows a documented competitive process with sealed submissions, evaluation by a panel against pre-set criteria, conflict declarations and independent review of single-source awards.</x:v>
+      </x:c>
+      <x:c r="P32" s="5" t="str">
+        <x:v>The procurement owner must require, above defined thresholds, that evaluation criteria and weightings are fixed and recorded before submissions are opened, submissions remain sealed until a scheduled opening witnessed by at least two people, evaluation is performed by a panel with signed conflict declarations, and single-source or emergency awards require documented justification and independent approval; a periodic analysis reviews award concentration, repeated near-identical pricing and rotating winners.</x:v>
+      </x:c>
+      <x:c r="Q32" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R32" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="5" t="str">
+        <x:v>MF-D7-Q05</x:v>
+      </x:c>
+      <x:c r="B33" s="5" t="str">
+        <x:v>D7-Q05</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str">
+        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E33" s="5" t="str">
+        <x:v>High-risk suppliers or third-party relationships are periodically monitored or reviewed.</x:v>
+      </x:c>
+      <x:c r="F33" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G33" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H33" s="5" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I33" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J33" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K33" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L33" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M33" s="5" t="str">
+        <x:v>Ongoing high-risk third-party monitoring was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N33" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O33" s="5" t="str">
+        <x:v>High-risk third parties are re-screened and performance-reviewed on a risk-based cycle covering ownership change, sanctions status, delivery performance, pricing drift and spend concentration.</x:v>
+      </x:c>
+      <x:c r="P33" s="5" t="str">
+        <x:v>The vendor-risk owner must define a risk-based monitoring cycle in which high-risk third parties are re-screened for ownership and sanctions change, reviewed for delivery and quality performance, validated for pricing drift against benchmark or contract, and analysed for spend concentration and unusual growth; findings requiring action are logged with owners, and failure to complete a cycle triggers escalation to the CFO.</x:v>
+      </x:c>
+      <x:c r="Q33" s="5" t="str">
+        <x:v>CFO / COO</x:v>
+      </x:c>
+      <x:c r="R33" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="5" t="str">
+        <x:v>MF-D7-Q06</x:v>
+      </x:c>
+      <x:c r="B34" s="5" t="str">
+        <x:v>D7-Q06</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="str">
+        <x:v>Third-Party and Supply Chain Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E34" s="5" t="str">
+        <x:v>Procurement or vendor-management activity is subject to oversight or periodic review.</x:v>
+      </x:c>
+      <x:c r="F34" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G34" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H34" s="5" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I34" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J34" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K34" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L34" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M34" s="5" t="str">
+        <x:v>Independent oversight of procurement and vendor management was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N34" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O34" s="5" t="str">
+        <x:v>An independent function periodically reviews procurement and vendor-master activity covering master-data changes, award patterns, spend outside contract and policy exceptions.</x:v>
+      </x:c>
+      <x:c r="P34" s="5" t="str">
+        <x:v>The audit committee must commission periodic independent review of procurement and vendor management covering all vendor-master creations and amendments with approver identity, award patterns by buyer and supplier, spend outside approved contracts or thresholds, use of emergency and single-source routes, and policy exception volumes by individual; findings are reported to governance with owners and due dates and tracked to closure.</x:v>
+      </x:c>
+      <x:c r="Q34" s="5" t="str">
+        <x:v>Audit Committee Chair / CFO</x:v>
+      </x:c>
+      <x:c r="R34" s="5" t="str">
+        <x:v>90 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="5" t="str">
+        <x:v>MF-D8-Q06</x:v>
+      </x:c>
+      <x:c r="B35" s="5" t="str">
+        <x:v>D8-Q06</x:v>
+      </x:c>
+      <x:c r="C35" s="5" t="str">
+        <x:v>D8</x:v>
+      </x:c>
+      <x:c r="D35" s="5" t="str">
+        <x:v>Digital and Identity Fraud Risk</x:v>
+      </x:c>
+      <x:c r="E35" s="5" t="str">
+        <x:v>Employees and users know how to report suspicious digital activity or account-security concerns.</x:v>
+      </x:c>
+      <x:c r="F35" s="5" t="str">
+        <x:v>Partially designed — Some elements exist, but implementation is incomplete, inconsistent or not evidenced.</x:v>
+      </x:c>
+      <x:c r="G35" s="5" t="str">
+        <x:v>cross_domain_dependency</x:v>
+      </x:c>
+      <x:c r="H35" s="5" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I35" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J35" s="5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="K35" s="5" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="L35" s="5" t="str">
+        <x:v>CROSS_DOMAIN_DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="M35" s="5" t="str">
+        <x:v>Reporting route for suspicious digital activity was self-assessed as "Partially designed" (Some elements exist, but implementation is incomplete, inconsistent or not evidenced; normalised score 40/100). This is self-reported and requires the listed operating evidence before it can be treated as verified.</x:v>
+      </x:c>
+      <x:c r="N35" s="5" t="str">
+        <x:v>This recorded response and its surrounding exposure make the control materially relevant.</x:v>
+      </x:c>
+      <x:c r="O35" s="5" t="str">
+        <x:v>Reporting routes are published for both staff and external users, monitored during defined hours with defined response times, and feed directly into monitoring and incident response.</x:v>
+      </x:c>
+      <x:c r="P35" s="5" t="str">
+        <x:v>The security operations owner must publish a clearly signposted route for staff and, where relevant, external users to report suspicious messages, unexpected account changes and suspected compromise, define monitored hours and target response times, connect reports directly into the alert triage and incident-response process, provide acknowledgement and outcome feedback, and track reporting volume and response time against target.</x:v>
+      </x:c>
+      <x:c r="Q35" s="5" t="str">
+        <x:v>Chief Technology Officer</x:v>
+      </x:c>
+      <x:c r="R35" s="5" t="str">
+        <x:v>60 days</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d37b41abaa4471d"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -3754,12 +3836,12 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R622908f68d524bcb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9eb526023d54e3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5640,12 +5722,12 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c9674437c664155"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R152c7c1448d04f3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9798,12 +9880,12 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3aa5c804debc48b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5851c2443fb47bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -11092,1159 +11174,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20510abd795e43a0"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>Agenda ID</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>Function</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>Question for the review</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>Linked finding</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="5" t="str">
-        <x:v>AGENDA-D7-Q04-OPERATION</x:v>
-      </x:c>
-      <x:c r="B2" s="5" t="str">
-        <x:v>Accounts Payable / Vendor Master</x:v>
-      </x:c>
-      <x:c r="C2" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Supplier payment processes include checks to reduce invoice manipulation, fake vendors, bank-detail changes or vendor impersonation", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D2" s="5" t="str">
-        <x:v>MF-D7-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="5" t="str">
-        <x:v>AGENDA-D4-Q07-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B3" s="5" t="str">
-        <x:v>Audit Committee</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Detection controls are periodically reviewed for effectiveness by management, risk, audit or another independent reviewer" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="str">
-        <x:v>MF-D4-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="5" t="str">
-        <x:v>AGENDA-D5-Q02-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="str">
-        <x:v>Audit Committee</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Employees know where and how to report suspected fraud or misconduct" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="str">
-        <x:v>MF-D5-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="5" t="str">
-        <x:v>AGENDA-D7-Q06-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="str">
-        <x:v>Audit Committee</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Procurement or vendor-management activity is subject to oversight or periodic review" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="str">
-        <x:v>MF-D7-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="5" t="str">
-        <x:v>AGENDA-D10-Q01-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="str">
-        <x:v>Audit Committee / Board</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "The organisation periodically reviews its fraud risks and control environment" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="str">
-        <x:v>MF-D10-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="5" t="str">
-        <x:v>AGENDA-D4-Q06-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="str">
-        <x:v>Audit Committee / Fraud-risk executive</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "People responsible for monitoring suspicious activity know when to escalate concerns and have authority to do so" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="str">
-        <x:v>MF-D4-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="5" t="str">
-        <x:v>AGENDA-D1-Q04-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>Audit Committee / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Management owns fraud risk, while internal audit or assurance functions provide independent review where they exist" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>MF-D1-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="5" t="str">
-        <x:v>AGENDA-D7-Q03-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>Audit Committee / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Employees are required to disclose and manage conflicts of interest involving suppliers or third parties" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>MF-D7-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="5" t="str">
-        <x:v>AGENDA-D2-Q01-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>Audit Committee / Risk Committee</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "The organisation has completed a structured fraud risk assessment within the past two years" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>MF-D2-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="5" t="str">
-        <x:v>AGENDA-D4-Q07-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>Audit Committee Chair</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Detection controls are periodically reviewed for effectiveness by management, risk, audit or another independent reviewer" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>MF-D4-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="5" t="str">
-        <x:v>AGENDA-D7-Q06-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B12" s="5" t="str">
-        <x:v>Audit Committee Chair / CFO</x:v>
-      </x:c>
-      <x:c r="C12" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Procurement or vendor-management activity is subject to oversight or periodic review" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D12" s="5" t="str">
-        <x:v>MF-D7-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="5" t="str">
-        <x:v>AGENDA-D1-Q01-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B13" s="5" t="str">
-        <x:v>Board / Audit Committee</x:v>
-      </x:c>
-      <x:c r="C13" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "A named senior owner is accountable for fraud risk management and has authority to drive action" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="str">
-        <x:v>MF-D1-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="5" t="str">
-        <x:v>AGENDA-D3-Q04-OPERATION</x:v>
-      </x:c>
-      <x:c r="B14" s="5" t="str">
-        <x:v>Business system owners</x:v>
-      </x:c>
-      <x:c r="C14" s="5" t="str">
-        <x:v>Who will deliver the exact design for "System and data access are granted based on role requirements and reviewed periodically", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="str">
-        <x:v>MF-D3-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="5" t="str">
-        <x:v>AGENDA-D1-Q04-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="str">
-        <x:v>CEO / Managing Director</x:v>
-      </x:c>
-      <x:c r="C15" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Management owns fraud risk, while internal audit or assurance functions provide independent review where they exist" by 30 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D15" s="5" t="str">
-        <x:v>MF-D1-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="5" t="str">
-        <x:v>AGENDA-D10-Q01-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B16" s="5" t="str">
-        <x:v>CEO / Managing Director</x:v>
-      </x:c>
-      <x:c r="C16" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "The organisation periodically reviews its fraud risks and control environment" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D16" s="5" t="str">
-        <x:v>MF-D10-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="5" t="str">
-        <x:v>AGENDA-D2-Q01-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B17" s="5" t="str">
-        <x:v>CEO / Managing Director</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "The organisation has completed a structured fraud risk assessment within the past two years" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D17" s="5" t="str">
-        <x:v>MF-D2-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="5" t="str">
-        <x:v>AGENDA-D7-Q04-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="str">
-        <x:v>CFO</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Supplier payment processes include checks to reduce invoice manipulation, fake vendors, bank-detail changes or vendor impersonation" by 30 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="str">
-        <x:v>MF-D7-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="5" t="str">
-        <x:v>AGENDA-D4-Q03-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B19" s="5" t="str">
-        <x:v>CFO / Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="C19" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Analytics, rules, reports or data checks are used to identify suspicious transactions, behaviour or control exceptions" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D19" s="5" t="str">
-        <x:v>MF-D4-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="5" t="str">
-        <x:v>AGENDA-D2-Q02-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B20" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="C20" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Fraud risks have been mapped across important processes such as procurement, payments, refunds, claims, stock, supplier management or service delivery" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D20" s="5" t="str">
-        <x:v>MF-D2-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="5" t="str">
-        <x:v>AGENDA-D3-Q03-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B21" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="C21" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Supplier onboarding includes checks on business information, ownership, banking details or other fraud-risk indicators" by 60 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D21" s="5" t="str">
-        <x:v>MF-D3-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="5" t="str">
-        <x:v>AGENDA-D4-Q01-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B22" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="C22" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "The organisation monitors transactions or operational activity for unusual patterns, anomalies or red flags" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D22" s="5" t="str">
-        <x:v>MF-D4-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="5" t="str">
-        <x:v>AGENDA-D7-Q01-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B23" s="5" t="str">
-        <x:v>CFO / COO</x:v>
-      </x:c>
-      <x:c r="C23" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Suppliers, contractors or other third parties are subject to due diligence before being engaged" by 60 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D23" s="5" t="str">
-        <x:v>MF-D7-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="5" t="str">
-        <x:v>AGENDA-D7-Q03-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B24" s="5" t="str">
-        <x:v>CFO / General Counsel</x:v>
-      </x:c>
-      <x:c r="C24" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Employees are required to disclose and manage conflicts of interest involving suppliers or third parties" by 60 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="str">
-        <x:v>MF-D7-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="5" t="str">
-        <x:v>AGENDA-D5-Q02-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B25" s="5" t="str">
-        <x:v>Chief People Officer / COO</x:v>
-      </x:c>
-      <x:c r="C25" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Employees know where and how to report suspected fraud or misconduct" by 30 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D25" s="5" t="str">
-        <x:v>MF-D5-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="5" t="str">
-        <x:v>AGENDA-D8-Q02-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B26" s="5" t="str">
-        <x:v>Chief Technology Officer</x:v>
-      </x:c>
-      <x:c r="C26" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Systems or digital platforms are monitored for suspicious activity such as unusual login, access, profile, transaction or account behaviour" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D26" s="5" t="str">
-        <x:v>MF-D8-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="5" t="str">
-        <x:v>AGENDA-D8-Q03-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B27" s="5" t="str">
-        <x:v>Chief Technology Officer / Chief People Officer</x:v>
-      </x:c>
-      <x:c r="C27" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Employees receive training on phishing, social engineering and digital impersonation attempts" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D27" s="5" t="str">
-        <x:v>MF-D8-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="5" t="str">
-        <x:v>AGENDA-D7-Q01-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B28" s="5" t="str">
-        <x:v>Compliance / Risk</x:v>
-      </x:c>
-      <x:c r="C28" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Suppliers, contractors or other third parties are subject to due diligence before being engaged" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D28" s="5" t="str">
-        <x:v>MF-D7-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="5" t="str">
-        <x:v>AGENDA-D7-Q03-OPERATION</x:v>
-      </x:c>
-      <x:c r="B29" s="5" t="str">
-        <x:v>Compliance with Human Resources</x:v>
-      </x:c>
-      <x:c r="C29" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Employees are required to disclose and manage conflicts of interest involving suppliers or third parties", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D29" s="5" t="str">
-        <x:v>MF-D7-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="5" t="str">
-        <x:v>AGENDA-D3-Q04-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B30" s="5" t="str">
-        <x:v>COO</x:v>
-      </x:c>
-      <x:c r="C30" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "System and data access are granted based on role requirements and reviewed periodically" by 60 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D30" s="5" t="str">
-        <x:v>MF-D3-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="5" t="str">
-        <x:v>AGENDA-D7-Q07-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B31" s="5" t="str">
-        <x:v>COO / CFO</x:v>
-      </x:c>
-      <x:c r="C31" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Fraud risks are considered when using agents, brokers, distributors, intermediaries, partners or outsourced service providers where relevant" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D31" s="5" t="str">
-        <x:v>MF-D7-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="5" t="str">
-        <x:v>AGENDA-D8-Q01-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B32" s="5" t="str">
-        <x:v>COO / CFO</x:v>
-      </x:c>
-      <x:c r="C32" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "The organisation verifies the identity of customers, users, employees, suppliers or counterparties where identity misuse could create fraud loss or harm" by 60 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D32" s="5" t="str">
-        <x:v>MF-D8-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="5" t="str">
-        <x:v>AGENDA-D5-Q01-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B33" s="5" t="str">
-        <x:v>COO / General Counsel</x:v>
-      </x:c>
-      <x:c r="C33" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "The organisation has a documented process for responding to suspected fraud incidents" by 30 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D33" s="5" t="str">
-        <x:v>MF-D5-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="5" t="str">
-        <x:v>AGENDA-D5-Q02-OPERATION</x:v>
-      </x:c>
-      <x:c r="B34" s="5" t="str">
-        <x:v>Ethics / Compliance lead</x:v>
-      </x:c>
-      <x:c r="C34" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Employees know where and how to report suspected fraud or misconduct", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D34" s="5" t="str">
-        <x:v>MF-D5-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="5" t="str">
-        <x:v>AGENDA-D7-Q04-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B35" s="5" t="str">
-        <x:v>Finance Control / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C35" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Supplier payment processes include checks to reduce invoice manipulation, fake vendors, bank-detail changes or vendor impersonation" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D35" s="5" t="str">
-        <x:v>MF-D7-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="5" t="str">
-        <x:v>AGENDA-D4-Q03-OPERATION</x:v>
-      </x:c>
-      <x:c r="B36" s="5" t="str">
-        <x:v>Fraud analytics owner</x:v>
-      </x:c>
-      <x:c r="C36" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Analytics, rules, reports or data checks are used to identify suspicious transactions, behaviour or control exceptions", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D36" s="5" t="str">
-        <x:v>MF-D4-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="5" t="str">
-        <x:v>AGENDA-D5-Q01-OPERATION</x:v>
-      </x:c>
-      <x:c r="B37" s="5" t="str">
-        <x:v>Fraud incident-response lead</x:v>
-      </x:c>
-      <x:c r="C37" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation has a documented process for responding to suspected fraud incidents", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D37" s="5" t="str">
-        <x:v>MF-D5-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="5" t="str">
-        <x:v>AGENDA-D4-Q01-OPERATION</x:v>
-      </x:c>
-      <x:c r="B38" s="5" t="str">
-        <x:v>Fraud monitoring owner</x:v>
-      </x:c>
-      <x:c r="C38" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation monitors transactions or operational activity for unusual patterns, anomalies or red flags", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D38" s="5" t="str">
-        <x:v>MF-D4-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="5" t="str">
-        <x:v>AGENDA-D4-Q06-OPERATION</x:v>
-      </x:c>
-      <x:c r="B39" s="5" t="str">
-        <x:v>Fraud monitoring team lead</x:v>
-      </x:c>
-      <x:c r="C39" s="5" t="str">
-        <x:v>Who will deliver the exact design for "People responsible for monitoring suspicious activity know when to escalate concerns and have authority to do so", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D39" s="5" t="str">
-        <x:v>MF-D4-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="5" t="str">
-        <x:v>AGENDA-D10-Q04-OPERATION</x:v>
-      </x:c>
-      <x:c r="B40" s="5" t="str">
-        <x:v>Fraud risk analyst or nominated owner</x:v>
-      </x:c>
-      <x:c r="C40" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation monitors fraud trends affecting its sector, geography, customer environment or supplier base", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D40" s="5" t="str">
-        <x:v>MF-D10-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="5" t="str">
-        <x:v>AGENDA-D2-Q06-OPERATION</x:v>
-      </x:c>
-      <x:c r="B41" s="5" t="str">
-        <x:v>Fraud risk analyst or nominated owner</x:v>
-      </x:c>
-      <x:c r="C41" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation monitors emerging fraud threats affecting its industry, geography or operating environment", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D41" s="5" t="str">
-        <x:v>MF-D2-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="5" t="str">
-        <x:v>AGENDA-D5-Q05-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B42" s="5" t="str">
-        <x:v>General Counsel / COO</x:v>
-      </x:c>
-      <x:c r="C42" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "Evidence linked to suspected fraud is identified, preserved and handled appropriately" by 60 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D42" s="5" t="str">
-        <x:v>MF-D5-Q05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="5" t="str">
-        <x:v>AGENDA-D10-Q01-OPERATION</x:v>
-      </x:c>
-      <x:c r="B43" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="C43" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation periodically reviews its fraud risks and control environment", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D43" s="5" t="str">
-        <x:v>MF-D10-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="5" t="str">
-        <x:v>AGENDA-D10-Q04-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B44" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="C44" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "The organisation monitors fraud trends affecting its sector, geography, customer environment or supplier base" by 90 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D44" s="5" t="str">
-        <x:v>MF-D10-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="5" t="str">
-        <x:v>AGENDA-D2-Q01-OPERATION</x:v>
-      </x:c>
-      <x:c r="B45" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="C45" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation has completed a structured fraud risk assessment within the past two years", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D45" s="5" t="str">
-        <x:v>MF-D2-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="5" t="str">
-        <x:v>AGENDA-D2-Q06-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B46" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="C46" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "The organisation monitors emerging fraud threats affecting its industry, geography or operating environment" by 60 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D46" s="5" t="str">
-        <x:v>MF-D2-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="5" t="str">
-        <x:v>AGENDA-D4-Q01-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B47" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="C47" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "The organisation monitors transactions or operational activity for unusual patterns, anomalies or red flags" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D47" s="5" t="str">
-        <x:v>MF-D4-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="5" t="str">
-        <x:v>AGENDA-D4-Q06-ACCOUNTABILITY</x:v>
-      </x:c>
-      <x:c r="B48" s="5" t="str">
-        <x:v>Head of Risk</x:v>
-      </x:c>
-      <x:c r="C48" s="5" t="str">
-        <x:v>Will you mandate and resource remediation of "People responsible for monitoring suspicious activity know when to escalate concerns and have authority to do so" by 30 days, and what delay threshold will you escalate?</x:v>
-      </x:c>
-      <x:c r="D48" s="5" t="str">
-        <x:v>MF-D4-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="5" t="str">
-        <x:v>AGENDA-D4-Q03-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B49" s="5" t="str">
-        <x:v>Head of Risk / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C49" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Analytics, rules, reports or data checks are used to identify suspicious transactions, behaviour or control exceptions" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D49" s="5" t="str">
-        <x:v>MF-D4-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="5" t="str">
-        <x:v>AGENDA-D1-Q04-OPERATION</x:v>
-      </x:c>
-      <x:c r="B50" s="5" t="str">
-        <x:v>Head of Risk and business control owners</x:v>
-      </x:c>
-      <x:c r="C50" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Management owns fraud risk, while internal audit or assurance functions provide independent review where they exist", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D50" s="5" t="str">
-        <x:v>MF-D1-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="5" t="str">
-        <x:v>AGENDA-D2-Q02-OPERATION</x:v>
-      </x:c>
-      <x:c r="B51" s="5" t="str">
-        <x:v>Head of Risk with named process owners</x:v>
-      </x:c>
-      <x:c r="C51" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Fraud risks have been mapped across important processes such as procurement, payments, refunds, claims, stock, supplier management or service delivery", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D51" s="5" t="str">
-        <x:v>MF-D2-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="5" t="str">
-        <x:v>AGENDA-D8-Q04-OPERATION</x:v>
-      </x:c>
-      <x:c r="B52" s="5" t="str">
-        <x:v>Identity and Access Management</x:v>
-      </x:c>
-      <x:c r="C52" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Access to sensitive digital systems, administrator rights and confidential data is restricted and reviewed", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D52" s="5" t="str">
-        <x:v>MF-D8-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="5" t="str">
-        <x:v>AGENDA-D8-Q04-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B53" s="5" t="str">
-        <x:v>Information Security / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C53" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Access to sensitive digital systems, administrator rights and confidential data is restricted and reviewed" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D53" s="5" t="str">
-        <x:v>MF-D8-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="5" t="str">
-        <x:v>AGENDA-D8-Q02-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B54" s="5" t="str">
-        <x:v>Information Security / Risk</x:v>
-      </x:c>
-      <x:c r="C54" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Systems or digital platforms are monitored for suspicious activity such as unusual login, access, profile, transaction or account behaviour" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D54" s="5" t="str">
-        <x:v>MF-D8-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="5" t="str">
-        <x:v>AGENDA-D8-Q07-OPERATION</x:v>
-      </x:c>
-      <x:c r="B55" s="5" t="str">
-        <x:v>Information Security with digital channel owners</x:v>
-      </x:c>
-      <x:c r="C55" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Emerging digital fraud risks relevant to the organisation's operations or sector are reviewed periodically", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D55" s="5" t="str">
-        <x:v>MF-D8-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="5" t="str">
-        <x:v>AGENDA-D7-Q02-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B56" s="5" t="str">
-        <x:v>Internal Audit / Risk</x:v>
-      </x:c>
-      <x:c r="C56" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Procurement processes include safeguards against collusion, manipulation, bid rigging or favouritism" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D56" s="5" t="str">
-        <x:v>MF-D7-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="5" t="str">
-        <x:v>AGENDA-D4-Q07-OPERATION</x:v>
-      </x:c>
-      <x:c r="B57" s="5" t="str">
-        <x:v>Internal Audit or independent reviewer</x:v>
-      </x:c>
-      <x:c r="C57" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Detection controls are periodically reviewed for effectiveness by management, risk, audit or another independent reviewer", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D57" s="5" t="str">
-        <x:v>MF-D4-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="5" t="str">
-        <x:v>AGENDA-D7-Q06-OPERATION</x:v>
-      </x:c>
-      <x:c r="B58" s="5" t="str">
-        <x:v>Internal Audit or independent reviewer</x:v>
-      </x:c>
-      <x:c r="C58" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Procurement or vendor-management activity is subject to oversight or periodic review", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D58" s="5" t="str">
-        <x:v>MF-D7-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="5" t="str">
-        <x:v>AGENDA-D5-Q04-OPERATION</x:v>
-      </x:c>
-      <x:c r="B59" s="5" t="str">
-        <x:v>Investigation lead</x:v>
-      </x:c>
-      <x:c r="C59" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Fraud investigations follow procedures that protect confidentiality, fairness, evidence and documentation", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D59" s="5" t="str">
-        <x:v>MF-D5-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="5" t="str">
-        <x:v>AGENDA-D5-Q05-OPERATION</x:v>
-      </x:c>
-      <x:c r="B60" s="5" t="str">
-        <x:v>Investigation lead / Evidence custodian</x:v>
-      </x:c>
-      <x:c r="C60" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Evidence linked to suspected fraud is identified, preserved and handled appropriately", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D60" s="5" t="str">
-        <x:v>MF-D5-Q05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="5" t="str">
-        <x:v>AGENDA-D5-Q05-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B61" s="5" t="str">
-        <x:v>Legal / Compliance</x:v>
-      </x:c>
-      <x:c r="C61" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Evidence linked to suspected fraud is identified, preserved and handled appropriately" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D61" s="5" t="str">
-        <x:v>MF-D5-Q05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="5" t="str">
-        <x:v>AGENDA-D5-Q04-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B62" s="5" t="str">
-        <x:v>Legal / Human Resources</x:v>
-      </x:c>
-      <x:c r="C62" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Fraud investigations follow procedures that protect confidentiality, fairness, evidence and documentation" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D62" s="5" t="str">
-        <x:v>MF-D5-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="5" t="str">
-        <x:v>AGENDA-D1-Q01-OPERATION</x:v>
-      </x:c>
-      <x:c r="B63" s="5" t="str">
-        <x:v>Named fraud-risk executive</x:v>
-      </x:c>
-      <x:c r="C63" s="5" t="str">
-        <x:v>Who will deliver the exact design for "A named senior owner is accountable for fraud risk management and has authority to drive action", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D63" s="5" t="str">
-        <x:v>MF-D1-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="5" t="str">
-        <x:v>AGENDA-D8-Q01-OPERATION</x:v>
-      </x:c>
-      <x:c r="B64" s="5" t="str">
-        <x:v>Process owners for onboarding and activation</x:v>
-      </x:c>
-      <x:c r="C64" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation verifies the identity of customers, users, employees, suppliers or counterparties where identity misuse could create fraud loss or harm", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D64" s="5" t="str">
-        <x:v>MF-D8-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="5" t="str">
-        <x:v>AGENDA-D3-Q03-OPERATION</x:v>
-      </x:c>
-      <x:c r="B65" s="5" t="str">
-        <x:v>Procurement / Vendor Master</x:v>
-      </x:c>
-      <x:c r="C65" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Supplier onboarding includes checks on business information, ownership, banking details or other fraud-risk indicators", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D65" s="5" t="str">
-        <x:v>MF-D3-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="5" t="str">
-        <x:v>AGENDA-D7-Q01-OPERATION</x:v>
-      </x:c>
-      <x:c r="B66" s="5" t="str">
-        <x:v>Procurement / Vendor Risk</x:v>
-      </x:c>
-      <x:c r="C66" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Suppliers, contractors or other third parties are subject to due diligence before being engaged", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D66" s="5" t="str">
-        <x:v>MF-D7-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="5" t="str">
-        <x:v>AGENDA-D7-Q02-OPERATION</x:v>
-      </x:c>
-      <x:c r="B67" s="5" t="str">
-        <x:v>Procurement lead</x:v>
-      </x:c>
-      <x:c r="C67" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Procurement processes include safeguards against collusion, manipulation, bid rigging or favouritism", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D67" s="5" t="str">
-        <x:v>MF-D7-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="5" t="str">
-        <x:v>AGENDA-D7-Q07-OPERATION</x:v>
-      </x:c>
-      <x:c r="B68" s="5" t="str">
-        <x:v>Relationship owner with Procurement</x:v>
-      </x:c>
-      <x:c r="C68" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Fraud risks are considered when using agents, brokers, distributors, intermediaries, partners or outsourced service providers where relevant", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D68" s="5" t="str">
-        <x:v>MF-D7-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="5" t="str">
-        <x:v>AGENDA-D3-Q03-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B69" s="5" t="str">
-        <x:v>Risk / Compliance</x:v>
-      </x:c>
-      <x:c r="C69" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Supplier onboarding includes checks on business information, ownership, banking details or other fraud-risk indicators" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D69" s="5" t="str">
-        <x:v>MF-D3-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="5" t="str">
-        <x:v>AGENDA-D8-Q01-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B70" s="5" t="str">
-        <x:v>Risk / Compliance</x:v>
-      </x:c>
-      <x:c r="C70" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "The organisation verifies the identity of customers, users, employees, suppliers or counterparties where identity misuse could create fraud loss or harm" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D70" s="5" t="str">
-        <x:v>MF-D8-Q01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="5" t="str">
-        <x:v>AGENDA-D3-Q04-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B71" s="5" t="str">
-        <x:v>Risk / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C71" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "System and data access are granted based on role requirements and reviewed periodically" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D71" s="5" t="str">
-        <x:v>MF-D3-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="5" t="str">
-        <x:v>AGENDA-D7-Q05-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B72" s="5" t="str">
-        <x:v>Risk / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C72" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "High-risk suppliers or third-party relationships are periodically monitored or reviewed" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D72" s="5" t="str">
-        <x:v>MF-D7-Q05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="5" t="str">
-        <x:v>AGENDA-D7-Q07-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B73" s="5" t="str">
-        <x:v>Risk / Legal</x:v>
-      </x:c>
-      <x:c r="C73" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Fraud risks are considered when using agents, brokers, distributors, intermediaries, partners or outsourced service providers where relevant" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D73" s="5" t="str">
-        <x:v>MF-D7-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="5" t="str">
-        <x:v>AGENDA-D10-Q04-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B74" s="5" t="str">
-        <x:v>Risk Committee</x:v>
-      </x:c>
-      <x:c r="C74" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "The organisation monitors fraud trends affecting its sector, geography, customer environment or supplier base" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D74" s="5" t="str">
-        <x:v>MF-D10-Q04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="5" t="str">
-        <x:v>AGENDA-D2-Q06-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B75" s="5" t="str">
-        <x:v>Risk Committee</x:v>
-      </x:c>
-      <x:c r="C75" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "The organisation monitors emerging fraud threats affecting its industry, geography or operating environment" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D75" s="5" t="str">
-        <x:v>MF-D2-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="5" t="str">
-        <x:v>AGENDA-D8-Q07-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B76" s="5" t="str">
-        <x:v>Risk Committee</x:v>
-      </x:c>
-      <x:c r="C76" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Emerging digital fraud risks relevant to the organisation's operations or sector are reviewed periodically" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D76" s="5" t="str">
-        <x:v>MF-D8-Q07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="5" t="str">
-        <x:v>AGENDA-D2-Q02-OVERSIGHT</x:v>
-      </x:c>
-      <x:c r="B77" s="5" t="str">
-        <x:v>Risk Committee / Internal Audit</x:v>
-      </x:c>
-      <x:c r="C77" s="5" t="str">
-        <x:v>How will you challenge remediation evidence for "Fraud risks have been mapped across important processes such as procurement, payments, refunds, claims, stock, supplier management or service delivery" and report exceptions independently?</x:v>
-      </x:c>
-      <x:c r="D77" s="5" t="str">
-        <x:v>MF-D2-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="5" t="str">
-        <x:v>AGENDA-D8-Q03-OPERATION</x:v>
-      </x:c>
-      <x:c r="B78" s="5" t="str">
-        <x:v>Security awareness owner</x:v>
-      </x:c>
-      <x:c r="C78" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Employees receive training on phishing, social engineering and digital impersonation attempts", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D78" s="5" t="str">
-        <x:v>MF-D8-Q03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="5" t="str">
-        <x:v>AGENDA-D8-Q02-OPERATION</x:v>
-      </x:c>
-      <x:c r="B79" s="5" t="str">
-        <x:v>Security monitoring / SOC</x:v>
-      </x:c>
-      <x:c r="C79" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Systems or digital platforms are monitored for suspicious activity such as unusual login, access, profile, transaction or account behaviour", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D79" s="5" t="str">
-        <x:v>MF-D8-Q02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="5" t="str">
-        <x:v>AGENDA-D8-Q06-OPERATION</x:v>
-      </x:c>
-      <x:c r="B80" s="5" t="str">
-        <x:v>Security operations</x:v>
-      </x:c>
-      <x:c r="C80" s="5" t="str">
-        <x:v>Who will deliver the exact design for "Employees and users know how to report suspicious digital activity or account-security concerns", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D80" s="5" t="str">
-        <x:v>MF-D8-Q06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="5" t="str">
-        <x:v>AGENDA-D8-Q08-OPERATION</x:v>
-      </x:c>
-      <x:c r="B81" s="5" t="str">
-        <x:v>Security operations with identity owners</x:v>
-      </x:c>
-      <x:c r="C81" s="5" t="str">
-        <x:v>Who will deliver the exact design for "The organisation can detect or investigate identity misuse, account takeover, impersonation or unauthorised profile changes where relevant", retain the evidence and prove effectiveness?</x:v>
-      </x:c>
-      <x:c r="D81" s="5" t="str">
-        <x:v>MF-D8-Q08</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3660f17e388b4c15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20e104162bcd4ac7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14784,7 +13714,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b0ede23c6f4700"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra748e20f0b114865"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15822,7 +14752,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd2ce54f22df40a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02d837d9461a4492"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/commercial-quality/essential-supporting-register.xlsx
+++ b/outputs/commercial-quality/essential-supporting-register.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4fb10810d5de444d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="R5cf82cdc45b04313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R11f8fbcf79034878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="4" r:id="Raecab667226546ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="5" r:id="R6cae350385664347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="6" r:id="R386285b7f29a4be3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="R12911279fa404978"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="R800e50ed325044ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5e8a5cdebb5b48eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="Rb1160ab1fdc84094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R753778972e1b455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="4" r:id="R8f47449f36754f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="5" r:id="R42bb644f1eda4e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="6" r:id="R379f53cd375d4e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="Rbb120915ea324443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="R38257009eb9147e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -72,8 +72,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReadmeTable" displayName="ReadmeTable" ref="A1:C6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:C6"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReadmeTable" displayName="ReadmeTable" ref="A1:C7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:C7"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Meaning"/>
@@ -133,9 +133,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ControlActionsTable" displayName="ControlActionsTable" ref="A1:Q35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:Q35"/>
-  <x:tableColumns count="17">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ControlActionsTable" displayName="ControlActionsTable" ref="A1:R35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:R35"/>
+  <x:tableColumns count="18">
     <x:tableColumn id="1" name="Control action ID"/>
     <x:tableColumn id="2" name="Primary question code"/>
     <x:tableColumn id="3" name="Contributing question codes"/>
@@ -149,10 +149,11 @@
     <x:tableColumn id="11" name="Oversight function"/>
     <x:tableColumn id="12" name="Target period"/>
     <x:tableColumn id="13" name="Escalation threshold"/>
-    <x:tableColumn id="14" name="Linked findings"/>
-    <x:tableColumn id="15" name="Linked risks"/>
-    <x:tableColumn id="16" name="Linked roadmap actions"/>
-    <x:tableColumn id="17" name="Aggregated"/>
+    <x:tableColumn id="14" name="Failure response"/>
+    <x:tableColumn id="15" name="Linked findings"/>
+    <x:tableColumn id="16" name="Linked risks"/>
+    <x:tableColumn id="17" name="Linked roadmap actions"/>
+    <x:tableColumn id="18" name="Aggregated"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -471,41 +472,52 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="str">
-        <x:v>How to read it</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="str">
-        <x:v>Customer-facing meaning comes first; technical references appear last.</x:v>
+        <x:v>Deterministic readiness</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="n">
+        <x:v>35.55</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>Question Trace retains the complete response universe.</x:v>
+        <x:v>Reactive</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="str">
-        <x:v>Date convention</x:v>
+        <x:v>How to read it</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>DD MMM YYYY</x:v>
+        <x:v>Customer-facing meaning comes first; technical references appear last.</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>No ISO timestamps in customer-facing cells</x:v>
+        <x:v>Question Trace retains the complete response universe.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="str">
+        <x:v>Date convention</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>DD MMM YYYY</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>No ISO timestamps in customer-facing cells</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="5" t="str">
         <x:v>Status boundary</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B7" s="5" t="str">
         <x:v>Recorded self-assessment is not independent validation.</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str">
+      <x:c r="C7" s="5" t="str">
         <x:v>Use the named evidence and effectiveness fields for follow-up.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7f33ddfbfd0473f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04fe82469b794308"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2497,7 +2509,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d37b41abaa4471d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra056ea4b0674492d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3812,7 +3824,7 @@
         <x:v>the assessed control design or operation does not meet the exact expected standard</x:v>
       </x:c>
       <x:c r="G32" s="5" t="str">
-        <x:v>digital attack methods evolve quickly, so controls designed for last year’s technique leave newly common methods such as session hijacking or synthetic identity unaddressed</x:v>
+        <x:v>digital attack methods evolve quickly, so controls designed for last year’s technique leave newly common methods such as session hijacking or identity misuse unaddressed</x:v>
       </x:c>
       <x:c r="H32" s="5" t="str">
         <x:v>Digital and Identity Fraud Risk: Initial / ad hoc — Some activity may occur informally or reactively, but it is not defined, owned or reliable</x:v>
@@ -3836,7 +3848,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9eb526023d54e3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3402c2b29fd24acf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3862,6 +3874,7 @@
     <x:col min="15" max="15" width="24" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="24" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -3905,15 +3918,18 @@
         <x:v>Escalation threshold</x:v>
       </x:c>
       <x:c r="N1" s="3" t="str">
+        <x:v>Failure response</x:v>
+      </x:c>
+      <x:c r="O1" s="3" t="str">
         <x:v>Linked findings</x:v>
       </x:c>
-      <x:c r="O1" s="3" t="str">
+      <x:c r="P1" s="3" t="str">
         <x:v>Linked risks</x:v>
       </x:c>
-      <x:c r="P1" s="3" t="str">
+      <x:c r="Q1" s="3" t="str">
         <x:v>Linked roadmap actions</x:v>
       </x:c>
-      <x:c r="Q1" s="3" t="str">
+      <x:c r="R1" s="3" t="str">
         <x:v>Aggregated</x:v>
       </x:c>
     </x:row>
@@ -3958,15 +3974,18 @@
         <x:v>Any assurance reviewer assigned operational ownership of the control under review.</x:v>
       </x:c>
       <x:c r="N2" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O2" s="5" t="str">
         <x:v>MF-D1-Q04</x:v>
       </x:c>
-      <x:c r="O2" s="5" t="str">
+      <x:c r="P2" s="5" t="str">
         <x:v>RISK-GOVERNANCE-ACCOUNTABILITY</x:v>
       </x:c>
-      <x:c r="P2" s="5" t="str">
+      <x:c r="Q2" s="5" t="str">
         <x:v>RA-D1-Q04</x:v>
       </x:c>
-      <x:c r="Q2" s="5" t="str">
+      <x:c r="R2" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4011,15 +4030,18 @@
         <x:v>Any supplier activated before verification or any ownership/conflict match unresolved.</x:v>
       </x:c>
       <x:c r="N3" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O3" s="5" t="str">
         <x:v>MF-D3-Q03</x:v>
       </x:c>
-      <x:c r="O3" s="5" t="str">
+      <x:c r="P3" s="5" t="str">
         <x:v>RISK-SUPPLIER-ONBOARDING</x:v>
       </x:c>
-      <x:c r="P3" s="5" t="str">
+      <x:c r="Q3" s="5" t="str">
         <x:v>RA-D3-Q03</x:v>
       </x:c>
-      <x:c r="Q3" s="5" t="str">
+      <x:c r="R3" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4064,15 +4086,18 @@
         <x:v>Any unverified change released, callback mismatch or attempt to bypass segregation.</x:v>
       </x:c>
       <x:c r="N4" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O4" s="5" t="str">
         <x:v>MF-D7-Q04</x:v>
       </x:c>
-      <x:c r="O4" s="5" t="str">
+      <x:c r="P4" s="5" t="str">
         <x:v>RISK-SUPPLIER-PAYMENT-REDIRECTION</x:v>
       </x:c>
-      <x:c r="P4" s="5" t="str">
+      <x:c r="Q4" s="5" t="str">
         <x:v>RA-D7-Q04</x:v>
       </x:c>
-      <x:c r="Q4" s="5" t="str">
+      <x:c r="R4" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4117,15 +4142,18 @@
         <x:v>Any unexplained custody gap, integrity mismatch or unauthorised repository access.</x:v>
       </x:c>
       <x:c r="N5" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O5" s="5" t="str">
         <x:v>MF-D5-Q05</x:v>
       </x:c>
-      <x:c r="O5" s="5" t="str">
+      <x:c r="P5" s="5" t="str">
         <x:v>RISK-EVIDENCE-INTEGRITY</x:v>
       </x:c>
-      <x:c r="P5" s="5" t="str">
+      <x:c r="Q5" s="5" t="str">
         <x:v>RA-D5-Q05</x:v>
       </x:c>
-      <x:c r="Q5" s="5" t="str">
+      <x:c r="R5" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4170,15 +4198,18 @@
         <x:v>Any material control action without an owner or more than 30 days overdue.</x:v>
       </x:c>
       <x:c r="N6" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O6" s="5" t="str">
         <x:v>MF-D1-Q01</x:v>
       </x:c>
-      <x:c r="O6" s="5" t="str">
+      <x:c r="P6" s="5" t="str">
         <x:v>RISK-GOVERNANCE-ACCOUNTABILITY</x:v>
       </x:c>
-      <x:c r="P6" s="5" t="str">
+      <x:c r="Q6" s="5" t="str">
         <x:v>RA-D1-Q01</x:v>
       </x:c>
-      <x:c r="Q6" s="5" t="str">
+      <x:c r="R6" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4223,15 +4254,18 @@
         <x:v>A material process unmonitored, or a monitoring cycle missed without escalation.</x:v>
       </x:c>
       <x:c r="N7" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O7" s="5" t="str">
         <x:v>MF-D4-Q01</x:v>
       </x:c>
-      <x:c r="O7" s="5" t="str">
+      <x:c r="P7" s="5" t="str">
         <x:v>RISK-CONTROL-D4-Q01</x:v>
       </x:c>
-      <x:c r="P7" s="5" t="str">
+      <x:c r="Q7" s="5" t="str">
         <x:v>RA-D4-Q01</x:v>
       </x:c>
-      <x:c r="Q7" s="5" t="str">
+      <x:c r="R7" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4276,15 +4310,18 @@
         <x:v>Activation before verification, an unapproved exception, or a sensitive change without re-verification.</x:v>
       </x:c>
       <x:c r="N8" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O8" s="5" t="str">
         <x:v>MF-D8-Q01</x:v>
       </x:c>
-      <x:c r="O8" s="5" t="str">
+      <x:c r="P8" s="5" t="str">
         <x:v>RISK-CONTROL-D8-Q01</x:v>
       </x:c>
-      <x:c r="P8" s="5" t="str">
+      <x:c r="Q8" s="5" t="str">
         <x:v>RA-D8-Q01</x:v>
       </x:c>
-      <x:c r="Q8" s="5" t="str">
+      <x:c r="R8" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4329,15 +4366,18 @@
         <x:v>Review overdue, or a key control found lapsed with no remediation owner.</x:v>
       </x:c>
       <x:c r="N9" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O9" s="5" t="str">
         <x:v>MF-D10-Q01</x:v>
       </x:c>
-      <x:c r="O9" s="5" t="str">
+      <x:c r="P9" s="5" t="str">
         <x:v>RISK-CONTROL-D10-Q01</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="str">
+      <x:c r="Q9" s="5" t="str">
         <x:v>RA-D10-Q01</x:v>
       </x:c>
-      <x:c r="Q9" s="5" t="str">
+      <x:c r="R9" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4382,15 +4422,18 @@
         <x:v>Assessment older than 24 months, or any unacceptable residual risk without a funded owner and due date.</x:v>
       </x:c>
       <x:c r="N10" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O10" s="5" t="str">
         <x:v>MF-D2-Q01</x:v>
       </x:c>
-      <x:c r="O10" s="5" t="str">
+      <x:c r="P10" s="5" t="str">
         <x:v>RISK-CONTROL-D2-Q01</x:v>
       </x:c>
-      <x:c r="P10" s="5" t="str">
+      <x:c r="Q10" s="5" t="str">
         <x:v>RA-D2-Q01</x:v>
       </x:c>
-      <x:c r="Q10" s="5" t="str">
+      <x:c r="R10" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4435,15 +4478,18 @@
         <x:v>Any missed quarterly review, unassigned account or removal overdue beyond 10 business days.</x:v>
       </x:c>
       <x:c r="N11" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O11" s="5" t="str">
         <x:v>MF-D3-Q04</x:v>
       </x:c>
-      <x:c r="O11" s="5" t="str">
+      <x:c r="P11" s="5" t="str">
         <x:v>RISK-UNAUTHORISED-ACCESS</x:v>
       </x:c>
-      <x:c r="P11" s="5" t="str">
+      <x:c r="Q11" s="5" t="str">
         <x:v>RA-D3-Q04</x:v>
       </x:c>
-      <x:c r="Q11" s="5" t="str">
+      <x:c r="R11" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4488,15 +4534,18 @@
         <x:v>Severe incident not escalated within four hours or annual tabletop overdue.</x:v>
       </x:c>
       <x:c r="N12" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O12" s="5" t="str">
         <x:v>MF-D5-Q01</x:v>
       </x:c>
-      <x:c r="O12" s="5" t="str">
+      <x:c r="P12" s="5" t="str">
         <x:v>RISK-INCIDENT-RESPONSE</x:v>
       </x:c>
-      <x:c r="P12" s="5" t="str">
+      <x:c r="Q12" s="5" t="str">
         <x:v>RA-D5-Q01</x:v>
       </x:c>
-      <x:c r="Q12" s="5" t="str">
+      <x:c r="R12" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4541,15 +4590,18 @@
         <x:v>Priority feed outage, high-risk alert outside SLA or confirmed compromise not escalated.</x:v>
       </x:c>
       <x:c r="N13" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O13" s="5" t="str">
         <x:v>MF-D8-Q02</x:v>
       </x:c>
-      <x:c r="O13" s="5" t="str">
+      <x:c r="P13" s="5" t="str">
         <x:v>RISK-DIGITAL-MISUSE</x:v>
       </x:c>
-      <x:c r="P13" s="5" t="str">
+      <x:c r="Q13" s="5" t="str">
         <x:v>RA-D8-Q02</x:v>
       </x:c>
-      <x:c r="Q13" s="5" t="str">
+      <x:c r="R13" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4594,15 +4646,18 @@
         <x:v>Any unknown or unjustified privileged account, missed recertification or leaver access beyond 24 hours.</x:v>
       </x:c>
       <x:c r="N14" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O14" s="5" t="str">
         <x:v>MF-D8-Q04</x:v>
       </x:c>
-      <x:c r="O14" s="5" t="str">
+      <x:c r="P14" s="5" t="str">
         <x:v>RISK-UNAUTHORISED-ACCESS</x:v>
       </x:c>
-      <x:c r="P14" s="5" t="str">
+      <x:c r="Q14" s="5" t="str">
         <x:v>RA-D8-Q04</x:v>
       </x:c>
-      <x:c r="Q14" s="5" t="str">
+      <x:c r="R14" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4647,15 +4702,18 @@
         <x:v>A priority scenario with no operating check, or rules unexecuted for a full cycle.</x:v>
       </x:c>
       <x:c r="N15" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O15" s="5" t="str">
         <x:v>MF-D4-Q03</x:v>
       </x:c>
-      <x:c r="O15" s="5" t="str">
+      <x:c r="P15" s="5" t="str">
         <x:v>RISK-CONTROL-D4-Q03</x:v>
       </x:c>
-      <x:c r="P15" s="5" t="str">
+      <x:c r="Q15" s="5" t="str">
         <x:v>RA-D4-Q03</x:v>
       </x:c>
-      <x:c r="Q15" s="5" t="str">
+      <x:c r="R15" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4700,15 +4758,18 @@
         <x:v>A suspected takeover that cannot be reconstructed from logs, or a material system without identity logging.</x:v>
       </x:c>
       <x:c r="N16" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O16" s="5" t="str">
         <x:v>MF-D8-Q08</x:v>
       </x:c>
-      <x:c r="O16" s="5" t="str">
+      <x:c r="P16" s="5" t="str">
         <x:v>RISK-CONTROL-D8-Q08</x:v>
       </x:c>
-      <x:c r="P16" s="5" t="str">
+      <x:c r="Q16" s="5" t="str">
         <x:v>RA-D8-Q08</x:v>
       </x:c>
-      <x:c r="Q16" s="5" t="str">
+      <x:c r="R16" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4753,15 +4814,18 @@
         <x:v>Any material process unmapped, or a mapped residual gap with no owner.</x:v>
       </x:c>
       <x:c r="N17" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O17" s="5" t="str">
         <x:v>MF-D2-Q02</x:v>
       </x:c>
-      <x:c r="O17" s="5" t="str">
+      <x:c r="P17" s="5" t="str">
         <x:v>RISK-CONTROL-D2-Q02</x:v>
       </x:c>
-      <x:c r="P17" s="5" t="str">
+      <x:c r="Q17" s="5" t="str">
         <x:v>RA-D2-Q02</x:v>
       </x:c>
-      <x:c r="Q17" s="5" t="str">
+      <x:c r="R17" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4806,15 +4870,18 @@
         <x:v>Any engagement before due diligence or unresolved ownership, sanctions or conflict match.</x:v>
       </x:c>
       <x:c r="N18" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O18" s="5" t="str">
         <x:v>MF-D7-Q01</x:v>
       </x:c>
-      <x:c r="O18" s="5" t="str">
+      <x:c r="P18" s="5" t="str">
         <x:v>RISK-SUPPLIER-ONBOARDING</x:v>
       </x:c>
-      <x:c r="P18" s="5" t="str">
+      <x:c r="Q18" s="5" t="str">
         <x:v>RA-D7-Q01</x:v>
       </x:c>
-      <x:c r="Q18" s="5" t="str">
+      <x:c r="R18" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4859,15 +4926,18 @@
         <x:v>Any high-risk alert unassigned after one business day or SLA breach rate above 5%.</x:v>
       </x:c>
       <x:c r="N19" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O19" s="5" t="str">
         <x:v>MF-D4-Q02</x:v>
       </x:c>
-      <x:c r="O19" s="5" t="str">
+      <x:c r="P19" s="5" t="str">
         <x:v>RISK-DETECTION-REVIEW</x:v>
       </x:c>
-      <x:c r="P19" s="5" t="str">
+      <x:c r="Q19" s="5" t="str">
         <x:v>RA-D4-Q02</x:v>
       </x:c>
-      <x:c r="Q19" s="5" t="str">
+      <x:c r="R19" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4912,15 +4982,18 @@
         <x:v>A cycle missed, or a sector trend matching internal losses with no control response.</x:v>
       </x:c>
       <x:c r="N20" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O20" s="5" t="str">
         <x:v>MF-D10-Q04</x:v>
       </x:c>
-      <x:c r="O20" s="5" t="str">
+      <x:c r="P20" s="5" t="str">
         <x:v>RISK-CONTROL-D10-Q04</x:v>
       </x:c>
-      <x:c r="P20" s="5" t="str">
+      <x:c r="Q20" s="5" t="str">
         <x:v>RA-D10-Q04</x:v>
       </x:c>
-      <x:c r="Q20" s="5" t="str">
+      <x:c r="R20" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -4965,15 +5038,18 @@
         <x:v>A qualifying matter escalated late, or an escalation routed only through an implicated manager.</x:v>
       </x:c>
       <x:c r="N21" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O21" s="5" t="str">
         <x:v>MF-D4-Q06</x:v>
       </x:c>
-      <x:c r="O21" s="5" t="str">
+      <x:c r="P21" s="5" t="str">
         <x:v>RISK-CONTROL-D4-Q06</x:v>
       </x:c>
-      <x:c r="P21" s="5" t="str">
+      <x:c r="Q21" s="5" t="str">
         <x:v>RA-D4-Q06</x:v>
       </x:c>
-      <x:c r="Q21" s="5" t="str">
+      <x:c r="R21" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5018,15 +5094,18 @@
         <x:v>A threat materialising as a loss after being logged without a decision, or a missed monitoring cycle.</x:v>
       </x:c>
       <x:c r="N22" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O22" s="5" t="str">
         <x:v>MF-D2-Q06</x:v>
       </x:c>
-      <x:c r="O22" s="5" t="str">
+      <x:c r="P22" s="5" t="str">
         <x:v>RISK-CONTROL-D2-Q06</x:v>
       </x:c>
-      <x:c r="P22" s="5" t="str">
+      <x:c r="Q22" s="5" t="str">
         <x:v>RA-D2-Q06</x:v>
       </x:c>
-      <x:c r="Q22" s="5" t="str">
+      <x:c r="R22" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5071,15 +5150,18 @@
         <x:v>A confirmed incident bypassing detection with no rule reassessment, or detection unchanged across a full review period despite new threats.</x:v>
       </x:c>
       <x:c r="N23" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O23" s="5" t="str">
         <x:v>MF-D4-Q04</x:v>
       </x:c>
-      <x:c r="O23" s="5" t="str">
+      <x:c r="P23" s="5" t="str">
         <x:v>RISK-CONTROL-D4-Q04</x:v>
       </x:c>
-      <x:c r="P23" s="5" t="str">
+      <x:c r="Q23" s="5" t="str">
         <x:v>RA-D4-Q04</x:v>
       </x:c>
-      <x:c r="Q23" s="5" t="str">
+      <x:c r="R23" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5124,15 +5206,18 @@
         <x:v>A material process with monitoring on only one threat class and no logged gap owner.</x:v>
       </x:c>
       <x:c r="N24" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O24" s="5" t="str">
         <x:v>MF-D4-Q05</x:v>
       </x:c>
-      <x:c r="O24" s="5" t="str">
+      <x:c r="P24" s="5" t="str">
         <x:v>RISK-CONTROL-D4-Q05</x:v>
       </x:c>
-      <x:c r="P24" s="5" t="str">
+      <x:c r="Q24" s="5" t="str">
         <x:v>RA-D4-Q05</x:v>
       </x:c>
-      <x:c r="Q24" s="5" t="str">
+      <x:c r="R24" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5177,15 +5262,18 @@
         <x:v>Any site or worker group below the awareness threshold, or reporting material not reaching non-desk staff.</x:v>
       </x:c>
       <x:c r="N25" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O25" s="5" t="str">
         <x:v>MF-D5-Q02</x:v>
       </x:c>
-      <x:c r="O25" s="5" t="str">
+      <x:c r="P25" s="5" t="str">
         <x:v>RISK-CONTROL-D5-Q02</x:v>
       </x:c>
-      <x:c r="P25" s="5" t="str">
+      <x:c r="Q25" s="5" t="str">
         <x:v>RA-D5-Q02</x:v>
       </x:c>
-      <x:c r="Q25" s="5" t="str">
+      <x:c r="R25" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5230,15 +5318,18 @@
         <x:v>An employee-supplier match not investigated, or a declared conflict with no management action.</x:v>
       </x:c>
       <x:c r="N26" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O26" s="5" t="str">
         <x:v>MF-D7-Q03</x:v>
       </x:c>
-      <x:c r="O26" s="5" t="str">
+      <x:c r="P26" s="5" t="str">
         <x:v>RISK-CONTROL-D7-Q03</x:v>
       </x:c>
-      <x:c r="P26" s="5" t="str">
+      <x:c r="Q26" s="5" t="str">
         <x:v>RA-D7-Q03</x:v>
       </x:c>
-      <x:c r="Q26" s="5" t="str">
+      <x:c r="R26" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5283,15 +5374,18 @@
         <x:v>An intermediary operating without contractual fraud obligations, undisclosed sub-contracting, or unreconciled delegated collections.</x:v>
       </x:c>
       <x:c r="N27" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O27" s="5" t="str">
         <x:v>MF-D7-Q07</x:v>
       </x:c>
-      <x:c r="O27" s="5" t="str">
+      <x:c r="P27" s="5" t="str">
         <x:v>RISK-CONTROL-D7-Q07</x:v>
       </x:c>
-      <x:c r="P27" s="5" t="str">
+      <x:c r="Q27" s="5" t="str">
         <x:v>RA-D7-Q07</x:v>
       </x:c>
-      <x:c r="Q27" s="5" t="str">
+      <x:c r="R27" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5336,15 +5430,18 @@
         <x:v>A high-risk role group with low report rate, or a real payment instruction actioned without out-of-band verification.</x:v>
       </x:c>
       <x:c r="N28" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O28" s="5" t="str">
         <x:v>MF-D8-Q03</x:v>
       </x:c>
-      <x:c r="O28" s="5" t="str">
+      <x:c r="P28" s="5" t="str">
         <x:v>RISK-CONTROL-D8-Q03</x:v>
       </x:c>
-      <x:c r="P28" s="5" t="str">
+      <x:c r="Q28" s="5" t="str">
         <x:v>RA-D8-Q03</x:v>
       </x:c>
-      <x:c r="Q28" s="5" t="str">
+      <x:c r="R28" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5389,15 +5486,18 @@
         <x:v>A review cycle missed, or a known sector-active method with no assessment.</x:v>
       </x:c>
       <x:c r="N29" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O29" s="5" t="str">
         <x:v>MF-D8-Q07</x:v>
       </x:c>
-      <x:c r="O29" s="5" t="str">
+      <x:c r="P29" s="5" t="str">
         <x:v>RISK-CONTROL-D8-Q07</x:v>
       </x:c>
-      <x:c r="P29" s="5" t="str">
+      <x:c r="Q29" s="5" t="str">
         <x:v>RA-D8-Q07</x:v>
       </x:c>
-      <x:c r="Q29" s="5" t="str">
+      <x:c r="R29" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5442,15 +5542,18 @@
         <x:v>Review overdue, or a finding overdue beyond its due date without governance escalation.</x:v>
       </x:c>
       <x:c r="N30" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O30" s="5" t="str">
         <x:v>MF-D4-Q07</x:v>
       </x:c>
-      <x:c r="O30" s="5" t="str">
+      <x:c r="P30" s="5" t="str">
         <x:v>RISK-CONTROL-D4-Q07</x:v>
       </x:c>
-      <x:c r="P30" s="5" t="str">
+      <x:c r="Q30" s="5" t="str">
         <x:v>RA-D4-Q07</x:v>
       </x:c>
-      <x:c r="Q30" s="5" t="str">
+      <x:c r="R30" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5495,15 +5598,18 @@
         <x:v>A confidentiality breach, an investigation without contemporaneous records, or a failed closure quality review.</x:v>
       </x:c>
       <x:c r="N31" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O31" s="5" t="str">
         <x:v>MF-D5-Q04</x:v>
       </x:c>
-      <x:c r="O31" s="5" t="str">
+      <x:c r="P31" s="5" t="str">
         <x:v>RISK-CONTROL-D5-Q04</x:v>
       </x:c>
-      <x:c r="P31" s="5" t="str">
+      <x:c r="Q31" s="5" t="str">
         <x:v>RA-D5-Q04</x:v>
       </x:c>
-      <x:c r="Q31" s="5" t="str">
+      <x:c r="R31" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5548,15 +5654,18 @@
         <x:v>Criteria set or changed after bid opening, an undeclared conflict, or unjustified single-source award.</x:v>
       </x:c>
       <x:c r="N32" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O32" s="5" t="str">
         <x:v>MF-D7-Q02</x:v>
       </x:c>
-      <x:c r="O32" s="5" t="str">
+      <x:c r="P32" s="5" t="str">
         <x:v>RISK-CONTROL-D7-Q02</x:v>
       </x:c>
-      <x:c r="P32" s="5" t="str">
+      <x:c r="Q32" s="5" t="str">
         <x:v>RA-D7-Q02</x:v>
       </x:c>
-      <x:c r="Q32" s="5" t="str">
+      <x:c r="R32" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5601,15 +5710,18 @@
         <x:v>A high-risk third party overdue for review, or an ownership change detected without reassessment.</x:v>
       </x:c>
       <x:c r="N33" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O33" s="5" t="str">
         <x:v>MF-D7-Q05</x:v>
       </x:c>
-      <x:c r="O33" s="5" t="str">
+      <x:c r="P33" s="5" t="str">
         <x:v>RISK-CONTROL-D7-Q05</x:v>
       </x:c>
-      <x:c r="P33" s="5" t="str">
+      <x:c r="Q33" s="5" t="str">
         <x:v>RA-D7-Q05</x:v>
       </x:c>
-      <x:c r="Q33" s="5" t="str">
+      <x:c r="R33" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5654,15 +5766,18 @@
         <x:v>Review overdue, or a concentration of exceptions by one individual not investigated.</x:v>
       </x:c>
       <x:c r="N34" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O34" s="5" t="str">
         <x:v>MF-D7-Q06</x:v>
       </x:c>
-      <x:c r="O34" s="5" t="str">
+      <x:c r="P34" s="5" t="str">
         <x:v>RISK-CONTROL-D7-Q06</x:v>
       </x:c>
-      <x:c r="P34" s="5" t="str">
+      <x:c r="Q34" s="5" t="str">
         <x:v>RA-D7-Q06</x:v>
       </x:c>
-      <x:c r="Q34" s="5" t="str">
+      <x:c r="R34" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
@@ -5707,22 +5822,25 @@
         <x:v>A suspected compromise report unactioned beyond target, or no route published for a live user-facing channel.</x:v>
       </x:c>
       <x:c r="N35" s="5" t="str">
+        <x:v>If the threshold is reached, record the exception, escalate to the oversight function and track closure evidence.</x:v>
+      </x:c>
+      <x:c r="O35" s="5" t="str">
         <x:v>MF-D8-Q06</x:v>
       </x:c>
-      <x:c r="O35" s="5" t="str">
+      <x:c r="P35" s="5" t="str">
         <x:v>RISK-CONTROL-D8-Q06</x:v>
       </x:c>
-      <x:c r="P35" s="5" t="str">
+      <x:c r="Q35" s="5" t="str">
         <x:v>RA-D8-Q06</x:v>
       </x:c>
-      <x:c r="Q35" s="5" t="str">
+      <x:c r="R35" s="5" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R152c7c1448d04f3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf23b700763bf4c05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9880,7 +9998,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5851c2443fb47bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72d8e7a79a5f4e76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11174,7 +11292,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20e104162bcd4ac7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb2c9c33b774ebc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13714,7 +13832,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra748e20f0b114865"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d63cc34a06a46c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14752,7 +14870,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02d837d9461a4492"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc674525afc4c4f67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/commercial-quality/essential-supporting-register.xlsx
+++ b/outputs/commercial-quality/essential-supporting-register.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5e8a5cdebb5b48eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="Rb1160ab1fdc84094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R753778972e1b455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="4" r:id="R8f47449f36754f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="5" r:id="R42bb644f1eda4e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="6" r:id="R379f53cd375d4e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="Rbb120915ea324443"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="R38257009eb9147e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5241328da710499c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="Rb230e4c0c922441f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R041581376e184fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="4" r:id="R155b5612ce1f46f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="5" r:id="R9301ac75756c4c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="6" r:id="R8d7c8a6ab5d04a82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="R3520ca58f2ab4b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="Ra8f6bd157d5248c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -517,7 +517,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04fe82469b794308"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dda75f9b7444d55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2509,7 +2509,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra056ea4b0674492d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1920e5eb0714d1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3848,7 +3848,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3402c2b29fd24acf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75ea49e41eaa4c31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5840,7 +5840,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf23b700763bf4c05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98697fc7759d42b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9998,7 +9998,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72d8e7a79a5f4e76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1dafc1d9cf74bf2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11292,7 +11292,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb2c9c33b774ebc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b4c90c812b147d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13832,7 +13832,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d63cc34a06a46c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81acb31561054a49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14870,7 +14870,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc674525afc4c4f67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R749f6187bccd4744"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/commercial-quality/essential-supporting-register.xlsx
+++ b/outputs/commercial-quality/essential-supporting-register.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5241328da710499c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="Rb230e4c0c922441f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R041581376e184fe9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="4" r:id="R155b5612ce1f46f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="5" r:id="R9301ac75756c4c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="6" r:id="R8d7c8a6ab5d04a82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="R3520ca58f2ab4b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="Ra8f6bd157d5248c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7c514e3da6664cb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="R36bfd850879c4ae8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R9a985ee5bef846b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Actions" sheetId="4" r:id="Ra26a7b6e11ce4026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Checklist" sheetId="5" r:id="Read80b8cab454de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="6" r:id="Re847b2e796b1421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Trace" sheetId="7" r:id="R8ea3bca6c2244683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Improvements" sheetId="8" r:id="R6b05ba5ef9684d02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -517,7 +517,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dda75f9b7444d55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6dedf4112e4967"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2509,7 +2509,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1920e5eb0714d1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f1729617c124211"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3848,7 +3848,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75ea49e41eaa4c31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebc615a9e6764bb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5840,7 +5840,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98697fc7759d42b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4cdc2a45d914c47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9998,7 +9998,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1dafc1d9cf74bf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1da3875327344545"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11292,7 +11292,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b4c90c812b147d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65aa65fad6b54675"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13832,7 +13832,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81acb31561054a49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64554d1681e44e3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14870,7 +14870,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R749f6187bccd4744"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae5192ddd5d54cfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>